--- a/EX1/Baseline_prediction_posteriors/LApredict/LaPredict_OS_detailed_results_0_85.xlsx
+++ b/EX1/Baseline_prediction_posteriors/LApredict/LaPredict_OS_detailed_results_0_85.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX1\Baseline_prediction_posteriors\LApredict\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D276FA4-5AAD-436D-9A6D-B336A3848C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E94B7E9-D73A-4390-9F58-99ABE075523F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19780" yWindow="3330" windowWidth="24910" windowHeight="14110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="test" sheetId="2" r:id="rId1"/>
+    <sheet name="valid" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$P$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">valid!$A$2:$O$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="17">
   <si>
     <t>Total Rows</t>
   </si>
@@ -84,9 +85,6 @@
   </si>
   <si>
     <t>recall fault-prone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVG test </t>
   </si>
   <si>
     <t>AVG Valid</t>
@@ -146,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -154,6 +152,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -455,8 +455,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q100"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CACD9AD-A31B-4DDD-B114-C53225B539D8}">
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -510,6 +510,659 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>4552</v>
+      </c>
+      <c r="B2">
+        <v>3707</v>
+      </c>
+      <c r="C2">
+        <v>3506</v>
+      </c>
+      <c r="D2">
+        <v>201</v>
+      </c>
+      <c r="E2">
+        <v>925</v>
+      </c>
+      <c r="F2">
+        <v>900</v>
+      </c>
+      <c r="G2">
+        <v>25</v>
+      </c>
+      <c r="H2">
+        <v>861</v>
+      </c>
+      <c r="I2">
+        <v>841</v>
+      </c>
+      <c r="J2">
+        <v>20</v>
+      </c>
+      <c r="K2">
+        <v>0.93081081081081085</v>
+      </c>
+      <c r="L2">
+        <v>0.93444444444444441</v>
+      </c>
+      <c r="M2">
+        <v>0.8</v>
+      </c>
+      <c r="N2">
+        <f t="shared" ref="N2:P9" si="0">H2/B2</f>
+        <v>0.23226328567574858</v>
+      </c>
+      <c r="O2">
+        <f t="shared" si="0"/>
+        <v>0.23987450085567599</v>
+      </c>
+      <c r="P2">
+        <f t="shared" si="0"/>
+        <v>9.950248756218906E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>4552</v>
+      </c>
+      <c r="B3">
+        <v>3707</v>
+      </c>
+      <c r="C3">
+        <v>3506</v>
+      </c>
+      <c r="D3">
+        <v>201</v>
+      </c>
+      <c r="E3">
+        <v>925</v>
+      </c>
+      <c r="F3">
+        <v>900</v>
+      </c>
+      <c r="G3">
+        <v>25</v>
+      </c>
+      <c r="H3">
+        <v>861</v>
+      </c>
+      <c r="I3">
+        <v>841</v>
+      </c>
+      <c r="J3">
+        <v>20</v>
+      </c>
+      <c r="K3">
+        <v>0.93081081081081085</v>
+      </c>
+      <c r="L3">
+        <v>0.93444444444444441</v>
+      </c>
+      <c r="M3">
+        <v>0.8</v>
+      </c>
+      <c r="N3">
+        <f t="shared" si="0"/>
+        <v>0.23226328567574858</v>
+      </c>
+      <c r="O3">
+        <f t="shared" si="0"/>
+        <v>0.23987450085567599</v>
+      </c>
+      <c r="P3">
+        <f t="shared" si="0"/>
+        <v>9.950248756218906E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>4552</v>
+      </c>
+      <c r="B4">
+        <v>3707</v>
+      </c>
+      <c r="C4">
+        <v>3506</v>
+      </c>
+      <c r="D4">
+        <v>201</v>
+      </c>
+      <c r="E4">
+        <v>925</v>
+      </c>
+      <c r="F4">
+        <v>900</v>
+      </c>
+      <c r="G4">
+        <v>25</v>
+      </c>
+      <c r="H4">
+        <v>861</v>
+      </c>
+      <c r="I4">
+        <v>841</v>
+      </c>
+      <c r="J4">
+        <v>20</v>
+      </c>
+      <c r="K4">
+        <v>0.93081081081081085</v>
+      </c>
+      <c r="L4">
+        <v>0.93444444444444441</v>
+      </c>
+      <c r="M4">
+        <v>0.8</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="0"/>
+        <v>0.23226328567574858</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="0"/>
+        <v>0.23987450085567599</v>
+      </c>
+      <c r="P4">
+        <f t="shared" si="0"/>
+        <v>9.950248756218906E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4552</v>
+      </c>
+      <c r="B5">
+        <v>3707</v>
+      </c>
+      <c r="C5">
+        <v>3506</v>
+      </c>
+      <c r="D5">
+        <v>201</v>
+      </c>
+      <c r="E5">
+        <v>925</v>
+      </c>
+      <c r="F5">
+        <v>900</v>
+      </c>
+      <c r="G5">
+        <v>25</v>
+      </c>
+      <c r="H5">
+        <v>861</v>
+      </c>
+      <c r="I5">
+        <v>841</v>
+      </c>
+      <c r="J5">
+        <v>20</v>
+      </c>
+      <c r="K5">
+        <v>0.93081081081081085</v>
+      </c>
+      <c r="L5">
+        <v>0.93444444444444441</v>
+      </c>
+      <c r="M5">
+        <v>0.8</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="0"/>
+        <v>0.23226328567574858</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="0"/>
+        <v>0.23987450085567599</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="0"/>
+        <v>9.950248756218906E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4552</v>
+      </c>
+      <c r="B6">
+        <v>3707</v>
+      </c>
+      <c r="C6">
+        <v>3506</v>
+      </c>
+      <c r="D6">
+        <v>201</v>
+      </c>
+      <c r="E6">
+        <v>925</v>
+      </c>
+      <c r="F6">
+        <v>900</v>
+      </c>
+      <c r="G6">
+        <v>25</v>
+      </c>
+      <c r="H6">
+        <v>861</v>
+      </c>
+      <c r="I6">
+        <v>841</v>
+      </c>
+      <c r="J6">
+        <v>20</v>
+      </c>
+      <c r="K6">
+        <v>0.93081081081081085</v>
+      </c>
+      <c r="L6">
+        <v>0.93444444444444441</v>
+      </c>
+      <c r="M6">
+        <v>0.8</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="0"/>
+        <v>0.23226328567574858</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="0"/>
+        <v>0.23987450085567599</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="0"/>
+        <v>9.950248756218906E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>4552</v>
+      </c>
+      <c r="B7">
+        <v>3707</v>
+      </c>
+      <c r="C7">
+        <v>3506</v>
+      </c>
+      <c r="D7">
+        <v>201</v>
+      </c>
+      <c r="E7">
+        <v>925</v>
+      </c>
+      <c r="F7">
+        <v>900</v>
+      </c>
+      <c r="G7">
+        <v>25</v>
+      </c>
+      <c r="H7">
+        <v>861</v>
+      </c>
+      <c r="I7">
+        <v>841</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>0.93081081081081085</v>
+      </c>
+      <c r="L7">
+        <v>0.93444444444444441</v>
+      </c>
+      <c r="M7">
+        <v>0.8</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="0"/>
+        <v>0.23226328567574858</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="0"/>
+        <v>0.23987450085567599</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="0"/>
+        <v>9.950248756218906E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>4552</v>
+      </c>
+      <c r="B8">
+        <v>3707</v>
+      </c>
+      <c r="C8">
+        <v>3506</v>
+      </c>
+      <c r="D8">
+        <v>201</v>
+      </c>
+      <c r="E8">
+        <v>925</v>
+      </c>
+      <c r="F8">
+        <v>900</v>
+      </c>
+      <c r="G8">
+        <v>25</v>
+      </c>
+      <c r="H8">
+        <v>861</v>
+      </c>
+      <c r="I8">
+        <v>841</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
+        <v>0.93081081081081085</v>
+      </c>
+      <c r="L8">
+        <v>0.93444444444444441</v>
+      </c>
+      <c r="M8">
+        <v>0.8</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="0"/>
+        <v>0.23226328567574858</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="0"/>
+        <v>0.23987450085567599</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="0"/>
+        <v>9.950248756218906E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>4552</v>
+      </c>
+      <c r="B9">
+        <v>3707</v>
+      </c>
+      <c r="C9">
+        <v>3506</v>
+      </c>
+      <c r="D9">
+        <v>201</v>
+      </c>
+      <c r="E9">
+        <v>925</v>
+      </c>
+      <c r="F9">
+        <v>900</v>
+      </c>
+      <c r="G9">
+        <v>25</v>
+      </c>
+      <c r="H9">
+        <v>861</v>
+      </c>
+      <c r="I9">
+        <v>841</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9">
+        <v>0.93081081081081085</v>
+      </c>
+      <c r="L9">
+        <v>0.93444444444444441</v>
+      </c>
+      <c r="M9">
+        <v>0.8</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="0"/>
+        <v>0.23226328567574858</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="0"/>
+        <v>0.23987450085567599</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="0"/>
+        <v>9.950248756218906E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>4552</v>
+      </c>
+      <c r="B10">
+        <v>3707</v>
+      </c>
+      <c r="C10">
+        <v>3506</v>
+      </c>
+      <c r="D10">
+        <v>201</v>
+      </c>
+      <c r="E10">
+        <v>925</v>
+      </c>
+      <c r="F10">
+        <v>900</v>
+      </c>
+      <c r="G10">
+        <v>25</v>
+      </c>
+      <c r="H10">
+        <v>861</v>
+      </c>
+      <c r="I10">
+        <v>841</v>
+      </c>
+      <c r="J10">
+        <v>20</v>
+      </c>
+      <c r="K10">
+        <v>0.93081081081081085</v>
+      </c>
+      <c r="L10">
+        <v>0.93444444444444441</v>
+      </c>
+      <c r="M10">
+        <v>0.8</v>
+      </c>
+      <c r="N10">
+        <f t="shared" ref="N10:N11" si="1">H10/B10</f>
+        <v>0.23226328567574858</v>
+      </c>
+      <c r="O10">
+        <f t="shared" ref="O10:O11" si="2">I10/C10</f>
+        <v>0.23987450085567599</v>
+      </c>
+      <c r="P10">
+        <f t="shared" ref="P10:P11" si="3">J10/D10</f>
+        <v>9.950248756218906E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>4552</v>
+      </c>
+      <c r="B11">
+        <v>3707</v>
+      </c>
+      <c r="C11">
+        <v>3506</v>
+      </c>
+      <c r="D11">
+        <v>201</v>
+      </c>
+      <c r="E11">
+        <v>925</v>
+      </c>
+      <c r="F11">
+        <v>900</v>
+      </c>
+      <c r="G11">
+        <v>25</v>
+      </c>
+      <c r="H11">
+        <v>861</v>
+      </c>
+      <c r="I11">
+        <v>841</v>
+      </c>
+      <c r="J11">
+        <v>20</v>
+      </c>
+      <c r="K11">
+        <v>0.93081081081081085</v>
+      </c>
+      <c r="L11">
+        <v>0.93444444444444441</v>
+      </c>
+      <c r="M11">
+        <v>0.8</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="1"/>
+        <v>0.23226328567574858</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="2"/>
+        <v>0.23987450085567599</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="3"/>
+        <v>9.950248756218906E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <f>AVERAGE(A2:A9)</f>
+        <v>4552</v>
+      </c>
+      <c r="B13">
+        <f t="shared" ref="B13:P13" si="4">AVERAGE(B2:B9)</f>
+        <v>3707</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="4"/>
+        <v>3506</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="4"/>
+        <v>201</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="4"/>
+        <v>925</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="4"/>
+        <v>900</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="4"/>
+        <v>25</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="4"/>
+        <v>861</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="4"/>
+        <v>841</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="4"/>
+        <v>0.93081081081081074</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="4"/>
+        <v>0.93444444444444463</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="4"/>
+        <v>0.79999999999999993</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="4"/>
+        <v>0.23226328567574855</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="4"/>
+        <v>0.23987450085567599</v>
+      </c>
+      <c r="P13">
+        <f t="shared" si="4"/>
+        <v>9.950248756218906E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P104"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -522,5187 +1175,5074 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1820</v>
+        <v>1389</v>
       </c>
       <c r="B3">
-        <v>1389</v>
+        <v>1295</v>
       </c>
       <c r="C3">
-        <v>1295</v>
+        <v>94</v>
       </c>
       <c r="D3">
-        <v>94</v>
+        <v>360</v>
       </c>
       <c r="E3">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="F3">
-        <v>350</v>
+        <v>10</v>
       </c>
       <c r="G3">
+        <v>336</v>
+      </c>
+      <c r="H3">
+        <v>330</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="K3">
+        <v>0.94285714285714284</v>
+      </c>
+      <c r="L3">
+        <v>0.6</v>
+      </c>
+      <c r="M3">
+        <f t="shared" ref="M3:M34" si="0">G3/A3</f>
+        <v>0.24190064794816415</v>
+      </c>
+      <c r="N3">
+        <f t="shared" ref="N3:N34" si="1">H3/B3</f>
+        <v>0.25482625482625482</v>
+      </c>
+      <c r="O3">
+        <f t="shared" ref="O3:O34" si="2">I3/C3</f>
+        <v>6.3829787234042548E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1360</v>
+      </c>
+      <c r="B4">
+        <v>1256</v>
+      </c>
+      <c r="C4">
+        <v>104</v>
+      </c>
+      <c r="D4">
+        <v>366</v>
+      </c>
+      <c r="E4">
+        <v>353</v>
+      </c>
+      <c r="F4">
+        <v>13</v>
+      </c>
+      <c r="G4">
+        <v>337</v>
+      </c>
+      <c r="H4">
+        <v>327</v>
+      </c>
+      <c r="I4">
         <v>10</v>
       </c>
-      <c r="H3">
-        <v>336</v>
-      </c>
-      <c r="I3">
-        <v>330</v>
-      </c>
-      <c r="J3">
-        <v>6</v>
-      </c>
-      <c r="K3">
-        <v>0.93333333333333335</v>
-      </c>
-      <c r="L3">
-        <v>0.94285714285714284</v>
-      </c>
-      <c r="M3">
-        <v>0.6</v>
-      </c>
-      <c r="N3">
-        <f t="shared" ref="N3:N34" si="0">H3/B3</f>
-        <v>0.24190064794816415</v>
-      </c>
-      <c r="O3">
-        <f t="shared" ref="O3:O34" si="1">I3/C3</f>
-        <v>0.25482625482625482</v>
-      </c>
-      <c r="P3">
-        <f t="shared" ref="P3:P34" si="2">J3/D3</f>
-        <v>6.3829787234042548E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1820</v>
-      </c>
-      <c r="B4">
-        <v>1360</v>
-      </c>
-      <c r="C4">
-        <v>1256</v>
-      </c>
-      <c r="D4">
-        <v>104</v>
-      </c>
-      <c r="E4">
-        <v>366</v>
-      </c>
-      <c r="F4">
-        <v>353</v>
-      </c>
-      <c r="G4">
-        <v>13</v>
-      </c>
-      <c r="H4">
-        <v>337</v>
-      </c>
-      <c r="I4">
-        <v>327</v>
-      </c>
       <c r="J4">
-        <v>10</v>
+        <v>0.92076502732240439</v>
       </c>
       <c r="K4">
-        <v>0.92076502732240439</v>
+        <v>0.92634560906515584</v>
       </c>
       <c r="L4">
-        <v>0.92634560906515584</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="M4">
-        <v>0.76923076923076927</v>
-      </c>
-      <c r="N4">
         <f t="shared" si="0"/>
         <v>0.24779411764705883</v>
       </c>
-      <c r="O4">
+      <c r="N4">
         <f t="shared" si="1"/>
         <v>0.26035031847133761</v>
       </c>
-      <c r="P4">
+      <c r="O4">
         <f t="shared" si="2"/>
         <v>9.6153846153846159E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>1820</v>
+        <v>1362</v>
       </c>
       <c r="B5">
-        <v>1362</v>
+        <v>1260</v>
       </c>
       <c r="C5">
-        <v>1260</v>
+        <v>102</v>
       </c>
       <c r="D5">
-        <v>102</v>
+        <v>350</v>
       </c>
       <c r="E5">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="F5">
-        <v>339</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>318</v>
       </c>
       <c r="H5">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="I5">
-        <v>312</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>0.90857142857142859</v>
       </c>
       <c r="K5">
-        <v>0.90857142857142859</v>
+        <v>0.92035398230088494</v>
       </c>
       <c r="L5">
-        <v>0.92035398230088494</v>
+        <v>0.54545454545454541</v>
       </c>
       <c r="M5">
-        <v>0.54545454545454541</v>
-      </c>
-      <c r="N5">
         <f t="shared" si="0"/>
         <v>0.23348017621145375</v>
       </c>
-      <c r="O5">
+      <c r="N5">
         <f t="shared" si="1"/>
         <v>0.24761904761904763</v>
       </c>
-      <c r="P5">
+      <c r="O5">
         <f t="shared" si="2"/>
         <v>5.8823529411764705E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>1820</v>
+        <v>1358</v>
       </c>
       <c r="B6">
-        <v>1358</v>
+        <v>1261</v>
       </c>
       <c r="C6">
-        <v>1261</v>
+        <v>97</v>
       </c>
       <c r="D6">
-        <v>97</v>
+        <v>386</v>
       </c>
       <c r="E6">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="F6">
-        <v>381</v>
+        <v>5</v>
       </c>
       <c r="G6">
+        <v>348</v>
+      </c>
+      <c r="H6">
+        <v>343</v>
+      </c>
+      <c r="I6">
         <v>5</v>
       </c>
-      <c r="H6">
-        <v>348</v>
-      </c>
-      <c r="I6">
-        <v>343</v>
-      </c>
       <c r="J6">
-        <v>5</v>
+        <v>0.9015544041450777</v>
       </c>
       <c r="K6">
-        <v>0.9015544041450777</v>
+        <v>0.90026246719160108</v>
       </c>
       <c r="L6">
-        <v>0.90026246719160108</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6">
         <f t="shared" si="0"/>
         <v>0.25625920471281294</v>
       </c>
-      <c r="O6">
+      <c r="N6">
         <f t="shared" si="1"/>
         <v>0.2720063441712926</v>
       </c>
-      <c r="P6">
+      <c r="O6">
         <f t="shared" si="2"/>
         <v>5.1546391752577317E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>1820</v>
+        <v>1324</v>
       </c>
       <c r="B7">
-        <v>1324</v>
+        <v>1218</v>
       </c>
       <c r="C7">
-        <v>1218</v>
+        <v>106</v>
       </c>
       <c r="D7">
-        <v>106</v>
+        <v>358</v>
       </c>
       <c r="E7">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="F7">
-        <v>349</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>9</v>
+        <v>317</v>
       </c>
       <c r="H7">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="I7">
-        <v>311</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>6</v>
+        <v>0.88547486033519551</v>
       </c>
       <c r="K7">
-        <v>0.88547486033519551</v>
+        <v>0.89111747851002865</v>
       </c>
       <c r="L7">
-        <v>0.89111747851002865</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="M7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="N7">
         <f t="shared" si="0"/>
         <v>0.23942598187311179</v>
       </c>
-      <c r="O7">
+      <c r="N7">
         <f t="shared" si="1"/>
         <v>0.25533661740558294</v>
       </c>
-      <c r="P7">
+      <c r="O7">
         <f t="shared" si="2"/>
         <v>5.6603773584905662E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1820</v>
+        <v>1358</v>
       </c>
       <c r="B8">
-        <v>1358</v>
+        <v>1267</v>
       </c>
       <c r="C8">
-        <v>1267</v>
+        <v>91</v>
       </c>
       <c r="D8">
-        <v>91</v>
+        <v>389</v>
       </c>
       <c r="E8">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="F8">
-        <v>380</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>9</v>
+        <v>353</v>
       </c>
       <c r="H8">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="I8">
-        <v>346</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>0.90745501285347041</v>
       </c>
       <c r="K8">
-        <v>0.90745501285347041</v>
+        <v>0.91052631578947374</v>
       </c>
       <c r="L8">
-        <v>0.91052631578947374</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="M8">
-        <v>0.77777777777777779</v>
-      </c>
-      <c r="N8">
         <f t="shared" si="0"/>
         <v>0.25994108983799707</v>
       </c>
-      <c r="O8">
+      <c r="N8">
         <f t="shared" si="1"/>
         <v>0.27308602999210735</v>
       </c>
-      <c r="P8">
+      <c r="O8">
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1820</v>
+        <v>1361</v>
       </c>
       <c r="B9">
-        <v>1361</v>
+        <v>1278</v>
       </c>
       <c r="C9">
-        <v>1278</v>
+        <v>83</v>
       </c>
       <c r="D9">
-        <v>83</v>
+        <v>349</v>
       </c>
       <c r="E9">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F9">
-        <v>346</v>
+        <v>3</v>
       </c>
       <c r="G9">
+        <v>328</v>
+      </c>
+      <c r="H9">
+        <v>325</v>
+      </c>
+      <c r="I9">
         <v>3</v>
       </c>
-      <c r="H9">
-        <v>328</v>
-      </c>
-      <c r="I9">
-        <v>325</v>
-      </c>
       <c r="J9">
-        <v>3</v>
+        <v>0.93982808022922637</v>
       </c>
       <c r="K9">
-        <v>0.93982808022922637</v>
+        <v>0.93930635838150289</v>
       </c>
       <c r="L9">
-        <v>0.93930635838150289</v>
+        <v>1</v>
       </c>
       <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9">
         <f t="shared" si="0"/>
         <v>0.24099926524614254</v>
       </c>
-      <c r="O9">
+      <c r="N9">
         <f t="shared" si="1"/>
         <v>0.25430359937402192</v>
       </c>
-      <c r="P9">
+      <c r="O9">
         <f t="shared" si="2"/>
         <v>3.614457831325301E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>1820</v>
+        <v>1376</v>
       </c>
       <c r="B10">
-        <v>1376</v>
+        <v>1283</v>
       </c>
       <c r="C10">
-        <v>1283</v>
+        <v>93</v>
       </c>
       <c r="D10">
-        <v>93</v>
+        <v>343</v>
       </c>
       <c r="E10">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="F10">
-        <v>339</v>
+        <v>4</v>
       </c>
       <c r="G10">
+        <v>316</v>
+      </c>
+      <c r="H10">
+        <v>312</v>
+      </c>
+      <c r="I10">
         <v>4</v>
       </c>
-      <c r="H10">
-        <v>316</v>
-      </c>
-      <c r="I10">
-        <v>312</v>
-      </c>
       <c r="J10">
-        <v>4</v>
+        <v>0.92128279883381925</v>
       </c>
       <c r="K10">
-        <v>0.92128279883381925</v>
+        <v>0.92035398230088494</v>
       </c>
       <c r="L10">
-        <v>0.92035398230088494</v>
+        <v>1</v>
       </c>
       <c r="M10">
-        <v>1</v>
-      </c>
-      <c r="N10">
         <f t="shared" si="0"/>
         <v>0.22965116279069767</v>
       </c>
-      <c r="O10">
+      <c r="N10">
         <f t="shared" si="1"/>
         <v>0.24318004676539362</v>
       </c>
-      <c r="P10">
+      <c r="O10">
         <f t="shared" si="2"/>
         <v>4.3010752688172046E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1820</v>
+        <v>1347</v>
       </c>
       <c r="B11">
-        <v>1347</v>
+        <v>1257</v>
       </c>
       <c r="C11">
-        <v>1257</v>
+        <v>90</v>
       </c>
       <c r="D11">
-        <v>90</v>
+        <v>381</v>
       </c>
       <c r="E11">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="F11">
-        <v>372</v>
+        <v>9</v>
       </c>
       <c r="G11">
-        <v>9</v>
+        <v>345</v>
       </c>
       <c r="H11">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I11">
-        <v>341</v>
+        <v>4</v>
       </c>
       <c r="J11">
-        <v>4</v>
+        <v>0.90551181102362199</v>
       </c>
       <c r="K11">
-        <v>0.90551181102362199</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="L11">
-        <v>0.91666666666666663</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="M11">
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="N11">
         <f t="shared" si="0"/>
         <v>0.25612472160356348</v>
       </c>
-      <c r="O11">
+      <c r="N11">
         <f t="shared" si="1"/>
         <v>0.27128082736674625</v>
       </c>
-      <c r="P11">
+      <c r="O11">
         <f t="shared" si="2"/>
         <v>4.4444444444444446E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1820</v>
+        <v>1370</v>
       </c>
       <c r="B12">
-        <v>1370</v>
+        <v>1261</v>
       </c>
       <c r="C12">
-        <v>1261</v>
+        <v>109</v>
       </c>
       <c r="D12">
-        <v>109</v>
+        <v>369</v>
       </c>
       <c r="E12">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="F12">
-        <v>357</v>
+        <v>12</v>
       </c>
       <c r="G12">
-        <v>12</v>
+        <v>327</v>
       </c>
       <c r="H12">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="I12">
-        <v>318</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>9</v>
+        <v>0.88617886178861793</v>
       </c>
       <c r="K12">
-        <v>0.88617886178861793</v>
+        <v>0.89075630252100846</v>
       </c>
       <c r="L12">
-        <v>0.89075630252100846</v>
+        <v>0.75</v>
       </c>
       <c r="M12">
-        <v>0.75</v>
-      </c>
-      <c r="N12">
         <f t="shared" si="0"/>
         <v>0.23868613138686132</v>
       </c>
-      <c r="O12">
+      <c r="N12">
         <f t="shared" si="1"/>
         <v>0.2521808088818398</v>
       </c>
-      <c r="P12">
+      <c r="O12">
         <f t="shared" si="2"/>
         <v>8.2568807339449546E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>1820</v>
+        <v>1355</v>
       </c>
       <c r="B13">
-        <v>1355</v>
+        <v>1262</v>
       </c>
       <c r="C13">
-        <v>1262</v>
+        <v>93</v>
       </c>
       <c r="D13">
-        <v>93</v>
+        <v>360</v>
       </c>
       <c r="E13">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="F13">
-        <v>350</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>10</v>
+        <v>325</v>
       </c>
       <c r="H13">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="I13">
-        <v>317</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>8</v>
+        <v>0.90277777777777779</v>
       </c>
       <c r="K13">
-        <v>0.90277777777777779</v>
+        <v>0.90571428571428569</v>
       </c>
       <c r="L13">
-        <v>0.90571428571428569</v>
+        <v>0.8</v>
       </c>
       <c r="M13">
-        <v>0.8</v>
-      </c>
-      <c r="N13">
         <f t="shared" si="0"/>
         <v>0.23985239852398524</v>
       </c>
-      <c r="O13">
+      <c r="N13">
         <f t="shared" si="1"/>
         <v>0.25118858954041207</v>
       </c>
-      <c r="P13">
+      <c r="O13">
         <f t="shared" si="2"/>
         <v>8.6021505376344093E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>1820</v>
+        <v>1372</v>
       </c>
       <c r="B14">
-        <v>1372</v>
+        <v>1265</v>
       </c>
       <c r="C14">
-        <v>1265</v>
+        <v>107</v>
       </c>
       <c r="D14">
-        <v>107</v>
+        <v>356</v>
       </c>
       <c r="E14">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="F14">
-        <v>348</v>
+        <v>8</v>
       </c>
       <c r="G14">
-        <v>8</v>
+        <v>330</v>
       </c>
       <c r="H14">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="I14">
-        <v>327</v>
+        <v>3</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>0.9269662921348315</v>
       </c>
       <c r="K14">
-        <v>0.9269662921348315</v>
+        <v>0.93965517241379315</v>
       </c>
       <c r="L14">
-        <v>0.93965517241379315</v>
+        <v>0.375</v>
       </c>
       <c r="M14">
-        <v>0.375</v>
-      </c>
-      <c r="N14">
         <f t="shared" si="0"/>
         <v>0.24052478134110788</v>
       </c>
-      <c r="O14">
+      <c r="N14">
         <f t="shared" si="1"/>
         <v>0.25849802371541503</v>
       </c>
-      <c r="P14">
+      <c r="O14">
         <f t="shared" si="2"/>
         <v>2.8037383177570093E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>1820</v>
+        <v>1374</v>
       </c>
       <c r="B15">
-        <v>1374</v>
+        <v>1259</v>
       </c>
       <c r="C15">
-        <v>1259</v>
+        <v>115</v>
       </c>
       <c r="D15">
-        <v>115</v>
+        <v>354</v>
       </c>
       <c r="E15">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="F15">
-        <v>345</v>
+        <v>9</v>
       </c>
       <c r="G15">
-        <v>9</v>
+        <v>324</v>
       </c>
       <c r="H15">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="I15">
-        <v>316</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>8</v>
+        <v>0.9152542372881356</v>
       </c>
       <c r="K15">
-        <v>0.9152542372881356</v>
+        <v>0.91594202898550725</v>
       </c>
       <c r="L15">
-        <v>0.91594202898550725</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="M15">
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="N15">
         <f t="shared" si="0"/>
         <v>0.23580786026200873</v>
       </c>
-      <c r="O15">
+      <c r="N15">
         <f t="shared" si="1"/>
         <v>0.25099285146942019</v>
       </c>
-      <c r="P15">
+      <c r="O15">
         <f t="shared" si="2"/>
         <v>6.9565217391304349E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>1820</v>
+        <v>1381</v>
       </c>
       <c r="B16">
-        <v>1381</v>
+        <v>1285</v>
       </c>
       <c r="C16">
-        <v>1285</v>
+        <v>96</v>
       </c>
       <c r="D16">
-        <v>96</v>
+        <v>367</v>
       </c>
       <c r="E16">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="F16">
-        <v>357</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>10</v>
+        <v>340</v>
       </c>
       <c r="H16">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="I16">
-        <v>333</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>7</v>
+        <v>0.92643051771117169</v>
       </c>
       <c r="K16">
-        <v>0.92643051771117169</v>
+        <v>0.9327731092436975</v>
       </c>
       <c r="L16">
-        <v>0.9327731092436975</v>
+        <v>0.7</v>
       </c>
       <c r="M16">
-        <v>0.7</v>
-      </c>
-      <c r="N16">
         <f t="shared" si="0"/>
         <v>0.24619840695148443</v>
       </c>
-      <c r="O16">
+      <c r="N16">
         <f t="shared" si="1"/>
         <v>0.25914396887159535</v>
       </c>
-      <c r="P16">
+      <c r="O16">
         <f t="shared" si="2"/>
         <v>7.2916666666666671E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>1820</v>
+        <v>1379</v>
       </c>
       <c r="B17">
-        <v>1379</v>
+        <v>1277</v>
       </c>
       <c r="C17">
-        <v>1277</v>
+        <v>102</v>
       </c>
       <c r="D17">
-        <v>102</v>
+        <v>372</v>
       </c>
       <c r="E17">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="F17">
-        <v>359</v>
+        <v>13</v>
       </c>
       <c r="G17">
-        <v>13</v>
+        <v>335</v>
       </c>
       <c r="H17">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="I17">
-        <v>325</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>10</v>
+        <v>0.90053763440860213</v>
       </c>
       <c r="K17">
-        <v>0.90053763440860213</v>
+        <v>0.90529247910863508</v>
       </c>
       <c r="L17">
-        <v>0.90529247910863508</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="M17">
-        <v>0.76923076923076927</v>
-      </c>
-      <c r="N17">
         <f t="shared" si="0"/>
         <v>0.24292965917331399</v>
       </c>
-      <c r="O17">
+      <c r="N17">
         <f t="shared" si="1"/>
         <v>0.25450274079874707</v>
       </c>
-      <c r="P17">
+      <c r="O17">
         <f t="shared" si="2"/>
         <v>9.8039215686274508E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>1820</v>
+        <v>1343</v>
       </c>
       <c r="B18">
-        <v>1343</v>
+        <v>1234</v>
       </c>
       <c r="C18">
-        <v>1234</v>
+        <v>109</v>
       </c>
       <c r="D18">
-        <v>109</v>
+        <v>356</v>
       </c>
       <c r="E18">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="F18">
-        <v>344</v>
+        <v>12</v>
       </c>
       <c r="G18">
-        <v>12</v>
+        <v>310</v>
       </c>
       <c r="H18">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="I18">
-        <v>302</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>8</v>
+        <v>0.8707865168539326</v>
       </c>
       <c r="K18">
-        <v>0.8707865168539326</v>
+        <v>0.87790697674418605</v>
       </c>
       <c r="L18">
-        <v>0.87790697674418605</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="M18">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="N18">
         <f t="shared" si="0"/>
         <v>0.23082650781831721</v>
       </c>
-      <c r="O18">
+      <c r="N18">
         <f t="shared" si="1"/>
         <v>0.24473257698541329</v>
       </c>
-      <c r="P18">
+      <c r="O18">
         <f t="shared" si="2"/>
         <v>7.3394495412844041E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>1820</v>
+        <v>1364</v>
       </c>
       <c r="B19">
-        <v>1364</v>
+        <v>1267</v>
       </c>
       <c r="C19">
-        <v>1267</v>
+        <v>97</v>
       </c>
       <c r="D19">
-        <v>97</v>
+        <v>354</v>
       </c>
       <c r="E19">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="F19">
-        <v>345</v>
+        <v>9</v>
       </c>
       <c r="G19">
-        <v>9</v>
+        <v>327</v>
       </c>
       <c r="H19">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="I19">
-        <v>319</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>8</v>
+        <v>0.92372881355932202</v>
       </c>
       <c r="K19">
-        <v>0.92372881355932202</v>
+        <v>0.92463768115942024</v>
       </c>
       <c r="L19">
-        <v>0.92463768115942024</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="M19">
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="N19">
         <f t="shared" si="0"/>
         <v>0.23973607038123168</v>
       </c>
-      <c r="O19">
+      <c r="N19">
         <f t="shared" si="1"/>
         <v>0.25177584846093132</v>
       </c>
-      <c r="P19">
+      <c r="O19">
         <f t="shared" si="2"/>
         <v>8.247422680412371E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>1820</v>
+        <v>1364</v>
       </c>
       <c r="B20">
-        <v>1364</v>
+        <v>1271</v>
       </c>
       <c r="C20">
-        <v>1271</v>
+        <v>93</v>
       </c>
       <c r="D20">
-        <v>93</v>
+        <v>335</v>
       </c>
       <c r="E20">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F20">
-        <v>327</v>
+        <v>8</v>
       </c>
       <c r="G20">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="H20">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="I20">
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>0.91044776119402981</v>
       </c>
       <c r="K20">
-        <v>0.91044776119402981</v>
+        <v>0.91743119266055051</v>
       </c>
       <c r="L20">
-        <v>0.91743119266055051</v>
+        <v>0.625</v>
       </c>
       <c r="M20">
-        <v>0.625</v>
-      </c>
-      <c r="N20">
         <f t="shared" si="0"/>
         <v>0.22360703812316715</v>
       </c>
-      <c r="O20">
+      <c r="N20">
         <f t="shared" si="1"/>
         <v>0.23603461841070023</v>
       </c>
-      <c r="P20">
+      <c r="O20">
         <f t="shared" si="2"/>
         <v>5.3763440860215055E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>1820</v>
+        <v>1357</v>
       </c>
       <c r="B21">
-        <v>1357</v>
+        <v>1258</v>
       </c>
       <c r="C21">
-        <v>1258</v>
+        <v>99</v>
       </c>
       <c r="D21">
-        <v>99</v>
+        <v>380</v>
       </c>
       <c r="E21">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="F21">
-        <v>362</v>
+        <v>18</v>
       </c>
       <c r="G21">
-        <v>18</v>
+        <v>335</v>
       </c>
       <c r="H21">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="I21">
-        <v>322</v>
+        <v>13</v>
       </c>
       <c r="J21">
-        <v>13</v>
+        <v>0.88157894736842102</v>
       </c>
       <c r="K21">
-        <v>0.88157894736842102</v>
+        <v>0.88950276243093918</v>
       </c>
       <c r="L21">
-        <v>0.88950276243093918</v>
+        <v>0.72222222222222221</v>
       </c>
       <c r="M21">
-        <v>0.72222222222222221</v>
-      </c>
-      <c r="N21">
         <f t="shared" si="0"/>
         <v>0.24686809137803981</v>
       </c>
-      <c r="O21">
+      <c r="N21">
         <f t="shared" si="1"/>
         <v>0.2559618441971383</v>
       </c>
-      <c r="P21">
+      <c r="O21">
         <f t="shared" si="2"/>
         <v>0.13131313131313133</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>1820</v>
+        <v>1383</v>
       </c>
       <c r="B22">
-        <v>1383</v>
+        <v>1298</v>
       </c>
       <c r="C22">
-        <v>1298</v>
+        <v>85</v>
       </c>
       <c r="D22">
-        <v>85</v>
+        <v>351</v>
       </c>
       <c r="E22">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F22">
-        <v>343</v>
+        <v>8</v>
       </c>
       <c r="G22">
-        <v>8</v>
+        <v>315</v>
       </c>
       <c r="H22">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="I22">
-        <v>309</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>6</v>
+        <v>0.89743589743589747</v>
       </c>
       <c r="K22">
-        <v>0.89743589743589747</v>
+        <v>0.9008746355685131</v>
       </c>
       <c r="L22">
-        <v>0.9008746355685131</v>
+        <v>0.75</v>
       </c>
       <c r="M22">
-        <v>0.75</v>
-      </c>
-      <c r="N22">
         <f t="shared" si="0"/>
         <v>0.22776572668112799</v>
       </c>
-      <c r="O22">
+      <c r="N22">
         <f t="shared" si="1"/>
         <v>0.23805855161787365</v>
       </c>
-      <c r="P22">
+      <c r="O22">
         <f t="shared" si="2"/>
         <v>7.0588235294117646E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>1820</v>
+        <v>1340</v>
       </c>
       <c r="B23">
-        <v>1340</v>
+        <v>1237</v>
       </c>
       <c r="C23">
-        <v>1237</v>
+        <v>103</v>
       </c>
       <c r="D23">
-        <v>103</v>
+        <v>360</v>
       </c>
       <c r="E23">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="F23">
-        <v>350</v>
+        <v>10</v>
       </c>
       <c r="G23">
-        <v>10</v>
+        <v>336</v>
       </c>
       <c r="H23">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I23">
-        <v>328</v>
+        <v>8</v>
       </c>
       <c r="J23">
-        <v>8</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="K23">
-        <v>0.93333333333333335</v>
+        <v>0.93714285714285717</v>
       </c>
       <c r="L23">
-        <v>0.93714285714285717</v>
+        <v>0.8</v>
       </c>
       <c r="M23">
-        <v>0.8</v>
-      </c>
-      <c r="N23">
         <f t="shared" si="0"/>
         <v>0.2507462686567164</v>
       </c>
-      <c r="O23">
+      <c r="N23">
         <f t="shared" si="1"/>
         <v>0.26515763945028292</v>
       </c>
-      <c r="P23">
+      <c r="O23">
         <f t="shared" si="2"/>
         <v>7.7669902912621352E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>1820</v>
+        <v>1366</v>
       </c>
       <c r="B24">
-        <v>1366</v>
+        <v>1260</v>
       </c>
       <c r="C24">
-        <v>1260</v>
+        <v>106</v>
       </c>
       <c r="D24">
-        <v>106</v>
+        <v>350</v>
       </c>
       <c r="E24">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="F24">
-        <v>341</v>
+        <v>9</v>
       </c>
       <c r="G24">
-        <v>9</v>
+        <v>322</v>
       </c>
       <c r="H24">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="I24">
-        <v>314</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>8</v>
+        <v>0.92</v>
       </c>
       <c r="K24">
-        <v>0.92</v>
+        <v>0.92082111436950143</v>
       </c>
       <c r="L24">
-        <v>0.92082111436950143</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="M24">
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="N24">
         <f t="shared" si="0"/>
         <v>0.23572474377745242</v>
       </c>
-      <c r="O24">
+      <c r="N24">
         <f t="shared" si="1"/>
         <v>0.24920634920634921</v>
       </c>
-      <c r="P24">
+      <c r="O24">
         <f t="shared" si="2"/>
         <v>7.5471698113207544E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>1820</v>
+        <v>1363</v>
       </c>
       <c r="B25">
-        <v>1363</v>
+        <v>1251</v>
       </c>
       <c r="C25">
-        <v>1251</v>
+        <v>112</v>
       </c>
       <c r="D25">
-        <v>112</v>
+        <v>373</v>
       </c>
       <c r="E25">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="F25">
-        <v>360</v>
+        <v>13</v>
       </c>
       <c r="G25">
-        <v>13</v>
+        <v>344</v>
       </c>
       <c r="H25">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="I25">
-        <v>332</v>
+        <v>12</v>
       </c>
       <c r="J25">
-        <v>12</v>
+        <v>0.92225201072386054</v>
       </c>
       <c r="K25">
-        <v>0.92225201072386054</v>
+        <v>0.92222222222222228</v>
       </c>
       <c r="L25">
-        <v>0.92222222222222228</v>
+        <v>0.92307692307692313</v>
       </c>
       <c r="M25">
-        <v>0.92307692307692313</v>
-      </c>
-      <c r="N25">
         <f t="shared" si="0"/>
         <v>0.2523844460748349</v>
       </c>
-      <c r="O25">
+      <c r="N25">
         <f t="shared" si="1"/>
         <v>0.2653876898481215</v>
       </c>
-      <c r="P25">
+      <c r="O25">
         <f t="shared" si="2"/>
         <v>0.10714285714285714</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>1820</v>
+        <v>1318</v>
       </c>
       <c r="B26">
-        <v>1318</v>
+        <v>1218</v>
       </c>
       <c r="C26">
-        <v>1218</v>
+        <v>100</v>
       </c>
       <c r="D26">
-        <v>100</v>
+        <v>364</v>
       </c>
       <c r="E26">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="F26">
-        <v>350</v>
+        <v>14</v>
       </c>
       <c r="G26">
-        <v>14</v>
+        <v>325</v>
       </c>
       <c r="H26">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="I26">
-        <v>314</v>
+        <v>11</v>
       </c>
       <c r="J26">
-        <v>11</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="K26">
-        <v>0.8928571428571429</v>
+        <v>0.89714285714285713</v>
       </c>
       <c r="L26">
-        <v>0.89714285714285713</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="M26">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="N26">
         <f t="shared" si="0"/>
         <v>0.24658573596358119</v>
       </c>
-      <c r="O26">
+      <c r="N26">
         <f t="shared" si="1"/>
         <v>0.25779967159277506</v>
       </c>
-      <c r="P26">
+      <c r="O26">
         <f t="shared" si="2"/>
         <v>0.11</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>1820</v>
+        <v>1376</v>
       </c>
       <c r="B27">
-        <v>1376</v>
+        <v>1272</v>
       </c>
       <c r="C27">
-        <v>1272</v>
+        <v>104</v>
       </c>
       <c r="D27">
-        <v>104</v>
+        <v>357</v>
       </c>
       <c r="E27">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="F27">
-        <v>346</v>
+        <v>11</v>
       </c>
       <c r="G27">
-        <v>11</v>
+        <v>327</v>
       </c>
       <c r="H27">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="I27">
-        <v>319</v>
+        <v>8</v>
       </c>
       <c r="J27">
-        <v>8</v>
+        <v>0.91596638655462181</v>
       </c>
       <c r="K27">
-        <v>0.91596638655462181</v>
+        <v>0.9219653179190751</v>
       </c>
       <c r="L27">
-        <v>0.9219653179190751</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="M27">
-        <v>0.72727272727272729</v>
-      </c>
-      <c r="N27">
         <f t="shared" si="0"/>
         <v>0.23764534883720931</v>
       </c>
-      <c r="O27">
+      <c r="N27">
         <f t="shared" si="1"/>
         <v>0.25078616352201261</v>
       </c>
-      <c r="P27">
+      <c r="O27">
         <f t="shared" si="2"/>
         <v>7.6923076923076927E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>1820</v>
+        <v>1350</v>
       </c>
       <c r="B28">
-        <v>1350</v>
+        <v>1250</v>
       </c>
       <c r="C28">
-        <v>1250</v>
+        <v>100</v>
       </c>
       <c r="D28">
-        <v>100</v>
+        <v>375</v>
       </c>
       <c r="E28">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="F28">
-        <v>358</v>
+        <v>17</v>
       </c>
       <c r="G28">
-        <v>17</v>
+        <v>329</v>
       </c>
       <c r="H28">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="I28">
-        <v>319</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>10</v>
+        <v>0.8773333333333333</v>
       </c>
       <c r="K28">
-        <v>0.8773333333333333</v>
+        <v>0.89106145251396651</v>
       </c>
       <c r="L28">
-        <v>0.89106145251396651</v>
+        <v>0.58823529411764708</v>
       </c>
       <c r="M28">
-        <v>0.58823529411764708</v>
-      </c>
-      <c r="N28">
         <f t="shared" si="0"/>
         <v>0.2437037037037037</v>
       </c>
-      <c r="O28">
+      <c r="N28">
         <f t="shared" si="1"/>
         <v>0.25519999999999998</v>
       </c>
-      <c r="P28">
+      <c r="O28">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>1820</v>
+        <v>1386</v>
       </c>
       <c r="B29">
-        <v>1386</v>
+        <v>1284</v>
       </c>
       <c r="C29">
-        <v>1284</v>
+        <v>102</v>
       </c>
       <c r="D29">
-        <v>102</v>
+        <v>368</v>
       </c>
       <c r="E29">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F29">
-        <v>361</v>
+        <v>7</v>
       </c>
       <c r="G29">
-        <v>7</v>
+        <v>335</v>
       </c>
       <c r="H29">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="I29">
-        <v>330</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>5</v>
+        <v>0.91032608695652173</v>
       </c>
       <c r="K29">
-        <v>0.91032608695652173</v>
+        <v>0.91412742382271472</v>
       </c>
       <c r="L29">
-        <v>0.91412742382271472</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="M29">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="N29">
         <f t="shared" si="0"/>
         <v>0.2417027417027417</v>
       </c>
-      <c r="O29">
+      <c r="N29">
         <f t="shared" si="1"/>
         <v>0.2570093457943925</v>
       </c>
-      <c r="P29">
+      <c r="O29">
         <f t="shared" si="2"/>
         <v>4.9019607843137254E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>1820</v>
+        <v>1361</v>
       </c>
       <c r="B30">
-        <v>1361</v>
+        <v>1274</v>
       </c>
       <c r="C30">
-        <v>1274</v>
+        <v>87</v>
       </c>
       <c r="D30">
-        <v>87</v>
+        <v>373</v>
       </c>
       <c r="E30">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="F30">
-        <v>356</v>
+        <v>17</v>
       </c>
       <c r="G30">
-        <v>17</v>
+        <v>336</v>
       </c>
       <c r="H30">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="I30">
-        <v>329</v>
+        <v>7</v>
       </c>
       <c r="J30">
-        <v>7</v>
+        <v>0.90080428954423597</v>
       </c>
       <c r="K30">
-        <v>0.90080428954423597</v>
+        <v>0.9241573033707865</v>
       </c>
       <c r="L30">
-        <v>0.9241573033707865</v>
+        <v>0.41176470588235292</v>
       </c>
       <c r="M30">
-        <v>0.41176470588235292</v>
-      </c>
-      <c r="N30">
         <f t="shared" si="0"/>
         <v>0.24687729610580456</v>
       </c>
-      <c r="O30">
+      <c r="N30">
         <f t="shared" si="1"/>
         <v>0.25824175824175827</v>
       </c>
-      <c r="P30">
+      <c r="O30">
         <f t="shared" si="2"/>
         <v>8.0459770114942528E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>1820</v>
+        <v>1358</v>
       </c>
       <c r="B31">
-        <v>1358</v>
+        <v>1272</v>
       </c>
       <c r="C31">
-        <v>1272</v>
+        <v>86</v>
       </c>
       <c r="D31">
-        <v>86</v>
+        <v>378</v>
       </c>
       <c r="E31">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="F31">
-        <v>371</v>
+        <v>7</v>
       </c>
       <c r="G31">
-        <v>7</v>
+        <v>343</v>
       </c>
       <c r="H31">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="I31">
-        <v>337</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>6</v>
+        <v>0.90740740740740744</v>
       </c>
       <c r="K31">
-        <v>0.90740740740740744</v>
+        <v>0.90835579514824794</v>
       </c>
       <c r="L31">
-        <v>0.90835579514824794</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="M31">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="N31">
         <f t="shared" si="0"/>
         <v>0.25257731958762886</v>
       </c>
-      <c r="O31">
+      <c r="N31">
         <f t="shared" si="1"/>
         <v>0.26493710691823902</v>
       </c>
-      <c r="P31">
+      <c r="O31">
         <f t="shared" si="2"/>
         <v>6.9767441860465115E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>1820</v>
+        <v>1358</v>
       </c>
       <c r="B32">
-        <v>1358</v>
+        <v>1266</v>
       </c>
       <c r="C32">
-        <v>1266</v>
+        <v>92</v>
       </c>
       <c r="D32">
-        <v>92</v>
+        <v>374</v>
       </c>
       <c r="E32">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="F32">
-        <v>360</v>
+        <v>14</v>
       </c>
       <c r="G32">
-        <v>14</v>
+        <v>338</v>
       </c>
       <c r="H32">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="I32">
-        <v>329</v>
+        <v>9</v>
       </c>
       <c r="J32">
-        <v>9</v>
+        <v>0.90374331550802134</v>
       </c>
       <c r="K32">
-        <v>0.90374331550802134</v>
+        <v>0.91388888888888886</v>
       </c>
       <c r="L32">
-        <v>0.91388888888888886</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="M32">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="N32">
         <f t="shared" si="0"/>
         <v>0.24889543446244478</v>
       </c>
-      <c r="O32">
+      <c r="N32">
         <f t="shared" si="1"/>
         <v>0.25987361769352291</v>
       </c>
-      <c r="P32">
+      <c r="O32">
         <f t="shared" si="2"/>
         <v>9.7826086956521743E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>1820</v>
+        <v>1362</v>
       </c>
       <c r="B33">
-        <v>1362</v>
+        <v>1256</v>
       </c>
       <c r="C33">
-        <v>1256</v>
+        <v>106</v>
       </c>
       <c r="D33">
-        <v>106</v>
+        <v>345</v>
       </c>
       <c r="E33">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="F33">
-        <v>330</v>
+        <v>15</v>
       </c>
       <c r="G33">
-        <v>15</v>
+        <v>308</v>
       </c>
       <c r="H33">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="I33">
-        <v>298</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>10</v>
+        <v>0.89275362318840579</v>
       </c>
       <c r="K33">
-        <v>0.89275362318840579</v>
+        <v>0.90303030303030307</v>
       </c>
       <c r="L33">
-        <v>0.90303030303030307</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="M33">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="N33">
         <f t="shared" si="0"/>
         <v>0.2261380323054332</v>
       </c>
-      <c r="O33">
+      <c r="N33">
         <f t="shared" si="1"/>
         <v>0.23726114649681529</v>
       </c>
-      <c r="P33">
+      <c r="O33">
         <f t="shared" si="2"/>
         <v>9.4339622641509441E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>1820</v>
+        <v>1345</v>
       </c>
       <c r="B34">
-        <v>1345</v>
+        <v>1247</v>
       </c>
       <c r="C34">
-        <v>1247</v>
+        <v>98</v>
       </c>
       <c r="D34">
-        <v>98</v>
+        <v>359</v>
       </c>
       <c r="E34">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="F34">
-        <v>349</v>
+        <v>10</v>
       </c>
       <c r="G34">
-        <v>10</v>
+        <v>331</v>
       </c>
       <c r="H34">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="I34">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="J34">
-        <v>8</v>
+        <v>0.92200557103064062</v>
       </c>
       <c r="K34">
-        <v>0.92200557103064062</v>
+        <v>0.92550143266475648</v>
       </c>
       <c r="L34">
-        <v>0.92550143266475648</v>
+        <v>0.8</v>
       </c>
       <c r="M34">
-        <v>0.8</v>
-      </c>
-      <c r="N34">
         <f t="shared" si="0"/>
         <v>0.24609665427509295</v>
       </c>
-      <c r="O34">
+      <c r="N34">
         <f t="shared" si="1"/>
         <v>0.25902165196471533</v>
       </c>
-      <c r="P34">
+      <c r="O34">
         <f t="shared" si="2"/>
         <v>8.1632653061224483E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>1820</v>
+        <v>1376</v>
       </c>
       <c r="B35">
-        <v>1376</v>
+        <v>1273</v>
       </c>
       <c r="C35">
-        <v>1273</v>
+        <v>103</v>
       </c>
       <c r="D35">
-        <v>103</v>
+        <v>377</v>
       </c>
       <c r="E35">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="F35">
-        <v>370</v>
+        <v>7</v>
       </c>
       <c r="G35">
-        <v>7</v>
+        <v>336</v>
       </c>
       <c r="H35">
+        <v>330</v>
+      </c>
+      <c r="I35">
+        <v>6</v>
+      </c>
+      <c r="J35">
+        <v>0.89124668435013266</v>
+      </c>
+      <c r="K35">
+        <v>0.89189189189189189</v>
+      </c>
+      <c r="L35">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="M35">
+        <f t="shared" ref="M35:M66" si="3">G35/A35</f>
+        <v>0.2441860465116279</v>
+      </c>
+      <c r="N35">
+        <f t="shared" ref="N35:N66" si="4">H35/B35</f>
+        <v>0.25923016496465046</v>
+      </c>
+      <c r="O35">
+        <f t="shared" ref="O35:O66" si="5">I35/C35</f>
+        <v>5.8252427184466021E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>1399</v>
+      </c>
+      <c r="B36">
+        <v>1299</v>
+      </c>
+      <c r="C36">
+        <v>100</v>
+      </c>
+      <c r="D36">
+        <v>349</v>
+      </c>
+      <c r="E36">
         <v>336</v>
       </c>
-      <c r="I35">
-        <v>330</v>
-      </c>
-      <c r="J35">
-        <v>6</v>
-      </c>
-      <c r="K35">
-        <v>0.89124668435013266</v>
-      </c>
-      <c r="L35">
-        <v>0.89189189189189189</v>
-      </c>
-      <c r="M35">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="N35">
-        <f t="shared" ref="N35:N66" si="3">H35/B35</f>
-        <v>0.2441860465116279</v>
-      </c>
-      <c r="O35">
-        <f t="shared" ref="O35:O66" si="4">I35/C35</f>
-        <v>0.25923016496465046</v>
-      </c>
-      <c r="P35">
-        <f t="shared" ref="P35:P66" si="5">J35/D35</f>
-        <v>5.8252427184466021E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>1820</v>
-      </c>
-      <c r="B36">
-        <v>1399</v>
-      </c>
-      <c r="C36">
-        <v>1299</v>
-      </c>
-      <c r="D36">
-        <v>100</v>
-      </c>
-      <c r="E36">
-        <v>349</v>
-      </c>
       <c r="F36">
-        <v>336</v>
+        <v>13</v>
       </c>
       <c r="G36">
-        <v>13</v>
+        <v>312</v>
       </c>
       <c r="H36">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="I36">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="J36">
-        <v>8</v>
+        <v>0.89398280802292263</v>
       </c>
       <c r="K36">
-        <v>0.89398280802292263</v>
+        <v>0.90476190476190477</v>
       </c>
       <c r="L36">
-        <v>0.90476190476190477</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="M36">
-        <v>0.61538461538461542</v>
-      </c>
-      <c r="N36">
         <f t="shared" si="3"/>
         <v>0.22301644031451037</v>
       </c>
-      <c r="O36">
+      <c r="N36">
         <f t="shared" si="4"/>
         <v>0.2340261739799846</v>
       </c>
-      <c r="P36">
+      <c r="O36">
         <f t="shared" si="5"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>1820</v>
+        <v>1295</v>
       </c>
       <c r="B37">
-        <v>1295</v>
+        <v>1196</v>
       </c>
       <c r="C37">
-        <v>1196</v>
+        <v>99</v>
       </c>
       <c r="D37">
-        <v>99</v>
+        <v>343</v>
       </c>
       <c r="E37">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="F37">
-        <v>332</v>
+        <v>11</v>
       </c>
       <c r="G37">
-        <v>11</v>
+        <v>303</v>
       </c>
       <c r="H37">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="I37">
-        <v>298</v>
+        <v>5</v>
       </c>
       <c r="J37">
-        <v>5</v>
+        <v>0.88338192419825068</v>
       </c>
       <c r="K37">
-        <v>0.88338192419825068</v>
+        <v>0.89759036144578308</v>
       </c>
       <c r="L37">
-        <v>0.89759036144578308</v>
+        <v>0.45454545454545447</v>
       </c>
       <c r="M37">
-        <v>0.45454545454545447</v>
-      </c>
-      <c r="N37">
         <f t="shared" si="3"/>
         <v>0.23397683397683397</v>
       </c>
-      <c r="O37">
+      <c r="N37">
         <f t="shared" si="4"/>
         <v>0.24916387959866221</v>
       </c>
-      <c r="P37">
+      <c r="O37">
         <f t="shared" si="5"/>
         <v>5.0505050505050504E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>1820</v>
+        <v>1317</v>
       </c>
       <c r="B38">
-        <v>1317</v>
+        <v>1242</v>
       </c>
       <c r="C38">
-        <v>1242</v>
+        <v>75</v>
       </c>
       <c r="D38">
-        <v>75</v>
+        <v>355</v>
       </c>
       <c r="E38">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="F38">
-        <v>350</v>
+        <v>5</v>
       </c>
       <c r="G38">
-        <v>5</v>
+        <v>327</v>
       </c>
       <c r="H38">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="I38">
-        <v>323</v>
+        <v>4</v>
       </c>
       <c r="J38">
-        <v>4</v>
+        <v>0.92112676056338028</v>
       </c>
       <c r="K38">
-        <v>0.92112676056338028</v>
+        <v>0.92285714285714282</v>
       </c>
       <c r="L38">
-        <v>0.92285714285714282</v>
+        <v>0.8</v>
       </c>
       <c r="M38">
-        <v>0.8</v>
-      </c>
-      <c r="N38">
         <f t="shared" si="3"/>
         <v>0.24829157175398633</v>
       </c>
-      <c r="O38">
+      <c r="N38">
         <f t="shared" si="4"/>
         <v>0.26006441223832527</v>
       </c>
-      <c r="P38">
+      <c r="O38">
         <f t="shared" si="5"/>
         <v>5.3333333333333337E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>1820</v>
+        <v>1368</v>
       </c>
       <c r="B39">
-        <v>1368</v>
+        <v>1262</v>
       </c>
       <c r="C39">
-        <v>1262</v>
+        <v>106</v>
       </c>
       <c r="D39">
-        <v>106</v>
+        <v>347</v>
       </c>
       <c r="E39">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="F39">
-        <v>344</v>
+        <v>3</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>312</v>
       </c>
       <c r="H39">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I39">
-        <v>311</v>
+        <v>1</v>
       </c>
       <c r="J39">
-        <v>1</v>
+        <v>0.89913544668587897</v>
       </c>
       <c r="K39">
-        <v>0.89913544668587897</v>
+        <v>0.90406976744186052</v>
       </c>
       <c r="L39">
-        <v>0.90406976744186052</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="M39">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="N39">
         <f t="shared" si="3"/>
         <v>0.22807017543859648</v>
       </c>
-      <c r="O39">
+      <c r="N39">
         <f t="shared" si="4"/>
         <v>0.24643423137876386</v>
       </c>
-      <c r="P39">
+      <c r="O39">
         <f t="shared" si="5"/>
         <v>9.433962264150943E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>1820</v>
+        <v>1355</v>
       </c>
       <c r="B40">
-        <v>1355</v>
+        <v>1256</v>
       </c>
       <c r="C40">
-        <v>1256</v>
+        <v>99</v>
       </c>
       <c r="D40">
-        <v>99</v>
+        <v>363</v>
       </c>
       <c r="E40">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="F40">
-        <v>354</v>
+        <v>9</v>
       </c>
       <c r="G40">
-        <v>9</v>
+        <v>319</v>
       </c>
       <c r="H40">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="I40">
-        <v>315</v>
+        <v>4</v>
       </c>
       <c r="J40">
-        <v>4</v>
+        <v>0.87878787878787878</v>
       </c>
       <c r="K40">
-        <v>0.87878787878787878</v>
+        <v>0.88983050847457623</v>
       </c>
       <c r="L40">
-        <v>0.88983050847457623</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="M40">
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="N40">
         <f t="shared" si="3"/>
         <v>0.23542435424354244</v>
       </c>
-      <c r="O40">
+      <c r="N40">
         <f t="shared" si="4"/>
         <v>0.25079617834394907</v>
       </c>
-      <c r="P40">
+      <c r="O40">
         <f t="shared" si="5"/>
         <v>4.0404040404040407E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>1820</v>
+        <v>1344</v>
       </c>
       <c r="B41">
-        <v>1344</v>
+        <v>1245</v>
       </c>
       <c r="C41">
-        <v>1245</v>
+        <v>99</v>
       </c>
       <c r="D41">
-        <v>99</v>
+        <v>348</v>
       </c>
       <c r="E41">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="F41">
-        <v>334</v>
+        <v>14</v>
       </c>
       <c r="G41">
-        <v>14</v>
+        <v>307</v>
       </c>
       <c r="H41">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="I41">
-        <v>299</v>
+        <v>8</v>
       </c>
       <c r="J41">
-        <v>8</v>
+        <v>0.88218390804597702</v>
       </c>
       <c r="K41">
-        <v>0.88218390804597702</v>
+        <v>0.89520958083832336</v>
       </c>
       <c r="L41">
-        <v>0.89520958083832336</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="M41">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="N41">
         <f t="shared" si="3"/>
         <v>0.22842261904761904</v>
       </c>
-      <c r="O41">
+      <c r="N41">
         <f t="shared" si="4"/>
         <v>0.24016064257028114</v>
       </c>
-      <c r="P41">
+      <c r="O41">
         <f t="shared" si="5"/>
         <v>8.0808080808080815E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>1820</v>
+        <v>1356</v>
       </c>
       <c r="B42">
-        <v>1356</v>
+        <v>1253</v>
       </c>
       <c r="C42">
-        <v>1253</v>
+        <v>103</v>
       </c>
       <c r="D42">
-        <v>103</v>
+        <v>329</v>
       </c>
       <c r="E42">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="F42">
-        <v>319</v>
+        <v>10</v>
       </c>
       <c r="G42">
-        <v>10</v>
+        <v>303</v>
       </c>
       <c r="H42">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="I42">
-        <v>296</v>
+        <v>7</v>
       </c>
       <c r="J42">
-        <v>7</v>
+        <v>0.92097264437689974</v>
       </c>
       <c r="K42">
-        <v>0.92097264437689974</v>
+        <v>0.92789968652037613</v>
       </c>
       <c r="L42">
-        <v>0.92789968652037613</v>
+        <v>0.7</v>
       </c>
       <c r="M42">
-        <v>0.7</v>
-      </c>
-      <c r="N42">
         <f t="shared" si="3"/>
         <v>0.22345132743362831</v>
       </c>
-      <c r="O42">
+      <c r="N42">
         <f t="shared" si="4"/>
         <v>0.23623304070231443</v>
       </c>
-      <c r="P42">
+      <c r="O42">
         <f t="shared" si="5"/>
         <v>6.7961165048543687E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>1820</v>
+        <v>1361</v>
       </c>
       <c r="B43">
-        <v>1361</v>
+        <v>1250</v>
       </c>
       <c r="C43">
-        <v>1250</v>
+        <v>111</v>
       </c>
       <c r="D43">
-        <v>111</v>
+        <v>359</v>
       </c>
       <c r="E43">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="F43">
-        <v>340</v>
+        <v>19</v>
       </c>
       <c r="G43">
-        <v>19</v>
+        <v>316</v>
       </c>
       <c r="H43">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="I43">
-        <v>306</v>
+        <v>10</v>
       </c>
       <c r="J43">
-        <v>10</v>
+        <v>0.88022284122562677</v>
       </c>
       <c r="K43">
-        <v>0.88022284122562677</v>
+        <v>0.9</v>
       </c>
       <c r="L43">
-        <v>0.9</v>
+        <v>0.52631578947368418</v>
       </c>
       <c r="M43">
-        <v>0.52631578947368418</v>
-      </c>
-      <c r="N43">
         <f t="shared" si="3"/>
         <v>0.23218221895664953</v>
       </c>
-      <c r="O43">
+      <c r="N43">
         <f t="shared" si="4"/>
         <v>0.24479999999999999</v>
       </c>
-      <c r="P43">
+      <c r="O43">
         <f t="shared" si="5"/>
         <v>9.0090090090090086E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>1820</v>
+        <v>1361</v>
       </c>
       <c r="B44">
-        <v>1361</v>
+        <v>1267</v>
       </c>
       <c r="C44">
-        <v>1267</v>
+        <v>94</v>
       </c>
       <c r="D44">
-        <v>94</v>
+        <v>371</v>
       </c>
       <c r="E44">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="F44">
-        <v>362</v>
+        <v>9</v>
       </c>
       <c r="G44">
-        <v>9</v>
+        <v>341</v>
       </c>
       <c r="H44">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="I44">
-        <v>335</v>
+        <v>6</v>
       </c>
       <c r="J44">
-        <v>6</v>
+        <v>0.91913746630727766</v>
       </c>
       <c r="K44">
-        <v>0.91913746630727766</v>
+        <v>0.925414364640884</v>
       </c>
       <c r="L44">
-        <v>0.925414364640884</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="M44">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="N44">
         <f t="shared" si="3"/>
         <v>0.2505510653930933</v>
       </c>
-      <c r="O44">
+      <c r="N44">
         <f t="shared" si="4"/>
         <v>0.26440410418310972</v>
       </c>
-      <c r="P44">
+      <c r="O44">
         <f t="shared" si="5"/>
         <v>6.3829787234042548E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>1821</v>
+        <v>1365</v>
       </c>
       <c r="B45">
-        <v>1365</v>
+        <v>1268</v>
       </c>
       <c r="C45">
-        <v>1268</v>
+        <v>97</v>
       </c>
       <c r="D45">
-        <v>97</v>
+        <v>395</v>
       </c>
       <c r="E45">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="F45">
-        <v>386</v>
+        <v>9</v>
       </c>
       <c r="G45">
-        <v>9</v>
+        <v>358</v>
       </c>
       <c r="H45">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="I45">
-        <v>350</v>
+        <v>8</v>
       </c>
       <c r="J45">
-        <v>8</v>
+        <v>0.90632911392405058</v>
       </c>
       <c r="K45">
-        <v>0.90632911392405058</v>
+        <v>0.90673575129533679</v>
       </c>
       <c r="L45">
-        <v>0.90673575129533679</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="M45">
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="N45">
         <f t="shared" si="3"/>
         <v>0.26227106227106228</v>
       </c>
-      <c r="O45">
+      <c r="N45">
         <f t="shared" si="4"/>
         <v>0.27602523659305994</v>
       </c>
-      <c r="P45">
+      <c r="O45">
         <f t="shared" si="5"/>
         <v>8.247422680412371E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>1821</v>
+        <v>1356</v>
       </c>
       <c r="B46">
-        <v>1356</v>
+        <v>1254</v>
       </c>
       <c r="C46">
-        <v>1254</v>
+        <v>102</v>
       </c>
       <c r="D46">
-        <v>102</v>
+        <v>327</v>
       </c>
       <c r="E46">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="F46">
-        <v>314</v>
+        <v>13</v>
       </c>
       <c r="G46">
-        <v>13</v>
+        <v>294</v>
       </c>
       <c r="H46">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="I46">
-        <v>286</v>
+        <v>8</v>
       </c>
       <c r="J46">
-        <v>8</v>
+        <v>0.8990825688073395</v>
       </c>
       <c r="K46">
-        <v>0.8990825688073395</v>
+        <v>0.91082802547770703</v>
       </c>
       <c r="L46">
-        <v>0.91082802547770703</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="M46">
-        <v>0.61538461538461542</v>
-      </c>
-      <c r="N46">
         <f t="shared" si="3"/>
         <v>0.2168141592920354</v>
       </c>
-      <c r="O46">
+      <c r="N46">
         <f t="shared" si="4"/>
         <v>0.22807017543859648</v>
       </c>
-      <c r="P46">
+      <c r="O46">
         <f t="shared" si="5"/>
         <v>7.8431372549019607E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>1821</v>
+        <v>1346</v>
       </c>
       <c r="B47">
-        <v>1346</v>
+        <v>1253</v>
       </c>
       <c r="C47">
-        <v>1253</v>
+        <v>93</v>
       </c>
       <c r="D47">
-        <v>93</v>
+        <v>387</v>
       </c>
       <c r="E47">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="F47">
-        <v>375</v>
+        <v>12</v>
       </c>
       <c r="G47">
-        <v>12</v>
+        <v>359</v>
       </c>
       <c r="H47">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="I47">
-        <v>353</v>
+        <v>6</v>
       </c>
       <c r="J47">
-        <v>6</v>
+        <v>0.92764857881136953</v>
       </c>
       <c r="K47">
-        <v>0.92764857881136953</v>
+        <v>0.94133333333333336</v>
       </c>
       <c r="L47">
-        <v>0.94133333333333336</v>
+        <v>0.5</v>
       </c>
       <c r="M47">
-        <v>0.5</v>
-      </c>
-      <c r="N47">
         <f t="shared" si="3"/>
         <v>0.26671619613670133</v>
       </c>
-      <c r="O47">
+      <c r="N47">
         <f t="shared" si="4"/>
         <v>0.28172386272944933</v>
       </c>
-      <c r="P47">
+      <c r="O47">
         <f t="shared" si="5"/>
         <v>6.4516129032258063E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>1821</v>
+        <v>1368</v>
       </c>
       <c r="B48">
-        <v>1368</v>
+        <v>1277</v>
       </c>
       <c r="C48">
-        <v>1277</v>
+        <v>91</v>
       </c>
       <c r="D48">
-        <v>91</v>
+        <v>367</v>
       </c>
       <c r="E48">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="F48">
-        <v>356</v>
+        <v>11</v>
       </c>
       <c r="G48">
-        <v>11</v>
+        <v>325</v>
       </c>
       <c r="H48">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="I48">
-        <v>317</v>
+        <v>8</v>
       </c>
       <c r="J48">
-        <v>8</v>
+        <v>0.88555858310626701</v>
       </c>
       <c r="K48">
-        <v>0.88555858310626701</v>
+        <v>0.8904494382022472</v>
       </c>
       <c r="L48">
-        <v>0.8904494382022472</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="M48">
-        <v>0.72727272727272729</v>
-      </c>
-      <c r="N48">
         <f t="shared" si="3"/>
         <v>0.23757309941520469</v>
       </c>
-      <c r="O48">
+      <c r="N48">
         <f t="shared" si="4"/>
         <v>0.24823805794831635</v>
       </c>
-      <c r="P48">
+      <c r="O48">
         <f t="shared" si="5"/>
         <v>8.7912087912087919E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>1821</v>
+        <v>1382</v>
       </c>
       <c r="B49">
-        <v>1382</v>
+        <v>1268</v>
       </c>
       <c r="C49">
-        <v>1268</v>
+        <v>114</v>
       </c>
       <c r="D49">
-        <v>114</v>
+        <v>383</v>
       </c>
       <c r="E49">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="F49">
-        <v>369</v>
+        <v>14</v>
       </c>
       <c r="G49">
-        <v>14</v>
+        <v>339</v>
       </c>
       <c r="H49">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="I49">
-        <v>328</v>
+        <v>11</v>
       </c>
       <c r="J49">
-        <v>11</v>
+        <v>0.88511749347258484</v>
       </c>
       <c r="K49">
-        <v>0.88511749347258484</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="L49">
-        <v>0.88888888888888884</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="M49">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="N49">
         <f t="shared" si="3"/>
         <v>0.24529667149059334</v>
       </c>
-      <c r="O49">
+      <c r="N49">
         <f t="shared" si="4"/>
         <v>0.25867507886435331</v>
       </c>
-      <c r="P49">
+      <c r="O49">
         <f t="shared" si="5"/>
         <v>9.6491228070175433E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>1821</v>
+        <v>1369</v>
       </c>
       <c r="B50">
-        <v>1369</v>
+        <v>1271</v>
       </c>
       <c r="C50">
-        <v>1271</v>
+        <v>98</v>
       </c>
       <c r="D50">
-        <v>98</v>
+        <v>359</v>
       </c>
       <c r="E50">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="F50">
-        <v>351</v>
+        <v>8</v>
       </c>
       <c r="G50">
-        <v>8</v>
+        <v>328</v>
       </c>
       <c r="H50">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="I50">
-        <v>323</v>
+        <v>5</v>
       </c>
       <c r="J50">
-        <v>5</v>
+        <v>0.91364902506963785</v>
       </c>
       <c r="K50">
-        <v>0.91364902506963785</v>
+        <v>0.92022792022792022</v>
       </c>
       <c r="L50">
-        <v>0.92022792022792022</v>
+        <v>0.625</v>
       </c>
       <c r="M50">
-        <v>0.625</v>
-      </c>
-      <c r="N50">
         <f t="shared" si="3"/>
         <v>0.239590942293645</v>
       </c>
-      <c r="O50">
+      <c r="N50">
         <f t="shared" si="4"/>
         <v>0.25413060582218727</v>
       </c>
-      <c r="P50">
+      <c r="O50">
         <f t="shared" si="5"/>
         <v>5.1020408163265307E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>1821</v>
+        <v>1392</v>
       </c>
       <c r="B51">
-        <v>1392</v>
+        <v>1283</v>
       </c>
       <c r="C51">
-        <v>1283</v>
+        <v>109</v>
       </c>
       <c r="D51">
-        <v>109</v>
+        <v>376</v>
       </c>
       <c r="E51">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="F51">
-        <v>363</v>
+        <v>13</v>
       </c>
       <c r="G51">
-        <v>13</v>
+        <v>335</v>
       </c>
       <c r="H51">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="I51">
-        <v>326</v>
+        <v>9</v>
       </c>
       <c r="J51">
-        <v>9</v>
+        <v>0.89095744680851063</v>
       </c>
       <c r="K51">
-        <v>0.89095744680851063</v>
+        <v>0.89807162534435259</v>
       </c>
       <c r="L51">
-        <v>0.89807162534435259</v>
+        <v>0.69230769230769229</v>
       </c>
       <c r="M51">
-        <v>0.69230769230769229</v>
-      </c>
-      <c r="N51">
         <f t="shared" si="3"/>
         <v>0.24066091954022989</v>
       </c>
-      <c r="O51">
+      <c r="N51">
         <f t="shared" si="4"/>
         <v>0.25409197194076383</v>
       </c>
-      <c r="P51">
+      <c r="O51">
         <f t="shared" si="5"/>
         <v>8.2568807339449546E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>1821</v>
+        <v>1342</v>
       </c>
       <c r="B52">
-        <v>1342</v>
+        <v>1242</v>
       </c>
       <c r="C52">
-        <v>1242</v>
+        <v>100</v>
       </c>
       <c r="D52">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E52">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="F52">
-        <v>382</v>
+        <v>18</v>
       </c>
       <c r="G52">
-        <v>18</v>
+        <v>364</v>
       </c>
       <c r="H52">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="I52">
-        <v>350</v>
+        <v>14</v>
       </c>
       <c r="J52">
-        <v>14</v>
+        <v>0.91</v>
       </c>
       <c r="K52">
-        <v>0.91</v>
+        <v>0.91623036649214662</v>
       </c>
       <c r="L52">
-        <v>0.91623036649214662</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="M52">
-        <v>0.77777777777777779</v>
-      </c>
-      <c r="N52">
         <f t="shared" si="3"/>
         <v>0.27123695976154993</v>
       </c>
-      <c r="O52">
+      <c r="N52">
         <f t="shared" si="4"/>
         <v>0.28180354267310787</v>
       </c>
-      <c r="P52">
+      <c r="O52">
         <f t="shared" si="5"/>
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>1821</v>
+        <v>1353</v>
       </c>
       <c r="B53">
-        <v>1353</v>
+        <v>1246</v>
       </c>
       <c r="C53">
-        <v>1246</v>
+        <v>107</v>
       </c>
       <c r="D53">
-        <v>107</v>
+        <v>378</v>
       </c>
       <c r="E53">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="F53">
-        <v>364</v>
+        <v>14</v>
       </c>
       <c r="G53">
-        <v>14</v>
+        <v>337</v>
       </c>
       <c r="H53">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="I53">
-        <v>328</v>
+        <v>9</v>
       </c>
       <c r="J53">
-        <v>9</v>
+        <v>0.89153439153439151</v>
       </c>
       <c r="K53">
-        <v>0.89153439153439151</v>
+        <v>0.90109890109890112</v>
       </c>
       <c r="L53">
-        <v>0.90109890109890112</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="M53">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="N53">
         <f t="shared" si="3"/>
         <v>0.24907612712490762</v>
       </c>
-      <c r="O53">
+      <c r="N53">
         <f t="shared" si="4"/>
         <v>0.26324237560192615</v>
       </c>
-      <c r="P53">
+      <c r="O53">
         <f t="shared" si="5"/>
         <v>8.4112149532710276E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>1821</v>
+        <v>1365</v>
       </c>
       <c r="B54">
-        <v>1365</v>
+        <v>1253</v>
       </c>
       <c r="C54">
-        <v>1253</v>
+        <v>112</v>
       </c>
       <c r="D54">
-        <v>112</v>
+        <v>380</v>
       </c>
       <c r="E54">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="F54">
-        <v>366</v>
+        <v>14</v>
       </c>
       <c r="G54">
-        <v>14</v>
+        <v>341</v>
       </c>
       <c r="H54">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="I54">
-        <v>332</v>
+        <v>9</v>
       </c>
       <c r="J54">
-        <v>9</v>
+        <v>0.89736842105263159</v>
       </c>
       <c r="K54">
-        <v>0.89736842105263159</v>
+        <v>0.90710382513661203</v>
       </c>
       <c r="L54">
-        <v>0.90710382513661203</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="M54">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="N54">
         <f t="shared" si="3"/>
         <v>0.24981684981684982</v>
       </c>
-      <c r="O54">
+      <c r="N54">
         <f t="shared" si="4"/>
         <v>0.26496408619313649</v>
       </c>
-      <c r="P54">
+      <c r="O54">
         <f t="shared" si="5"/>
         <v>8.0357142857142863E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>1821</v>
+        <v>1361</v>
       </c>
       <c r="B55">
-        <v>1361</v>
+        <v>1255</v>
       </c>
       <c r="C55">
-        <v>1255</v>
+        <v>106</v>
       </c>
       <c r="D55">
-        <v>106</v>
+        <v>351</v>
       </c>
       <c r="E55">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="F55">
-        <v>346</v>
+        <v>5</v>
       </c>
       <c r="G55">
-        <v>5</v>
+        <v>321</v>
       </c>
       <c r="H55">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="I55">
-        <v>317</v>
+        <v>4</v>
       </c>
       <c r="J55">
-        <v>4</v>
+        <v>0.9145299145299145</v>
       </c>
       <c r="K55">
-        <v>0.9145299145299145</v>
+        <v>0.91618497109826591</v>
       </c>
       <c r="L55">
-        <v>0.91618497109826591</v>
+        <v>0.8</v>
       </c>
       <c r="M55">
-        <v>0.8</v>
-      </c>
-      <c r="N55">
         <f t="shared" si="3"/>
         <v>0.23585598824393827</v>
       </c>
-      <c r="O55">
+      <c r="N55">
         <f t="shared" si="4"/>
         <v>0.25258964143426293</v>
       </c>
-      <c r="P55">
+      <c r="O55">
         <f t="shared" si="5"/>
         <v>3.7735849056603772E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>1821</v>
+        <v>1348</v>
       </c>
       <c r="B56">
-        <v>1348</v>
+        <v>1262</v>
       </c>
       <c r="C56">
-        <v>1262</v>
+        <v>86</v>
       </c>
       <c r="D56">
-        <v>86</v>
+        <v>384</v>
       </c>
       <c r="E56">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="F56">
-        <v>372</v>
+        <v>12</v>
       </c>
       <c r="G56">
-        <v>12</v>
+        <v>347</v>
       </c>
       <c r="H56">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="I56">
-        <v>341</v>
+        <v>6</v>
       </c>
       <c r="J56">
-        <v>6</v>
+        <v>0.90364583333333337</v>
       </c>
       <c r="K56">
-        <v>0.90364583333333337</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="L56">
-        <v>0.91666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="M56">
-        <v>0.5</v>
-      </c>
-      <c r="N56">
         <f t="shared" si="3"/>
         <v>0.25741839762611274</v>
       </c>
-      <c r="O56">
+      <c r="N56">
         <f t="shared" si="4"/>
         <v>0.27020602218700474</v>
       </c>
-      <c r="P56">
+      <c r="O56">
         <f t="shared" si="5"/>
         <v>6.9767441860465115E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>1821</v>
+        <v>1346</v>
       </c>
       <c r="B57">
-        <v>1346</v>
+        <v>1256</v>
       </c>
       <c r="C57">
-        <v>1256</v>
+        <v>90</v>
       </c>
       <c r="D57">
-        <v>90</v>
+        <v>377</v>
       </c>
       <c r="E57">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="F57">
-        <v>367</v>
+        <v>10</v>
       </c>
       <c r="G57">
-        <v>10</v>
+        <v>342</v>
       </c>
       <c r="H57">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="I57">
-        <v>336</v>
+        <v>6</v>
       </c>
       <c r="J57">
-        <v>6</v>
+        <v>0.90716180371352784</v>
       </c>
       <c r="K57">
-        <v>0.90716180371352784</v>
+        <v>0.91553133514986373</v>
       </c>
       <c r="L57">
-        <v>0.91553133514986373</v>
+        <v>0.6</v>
       </c>
       <c r="M57">
-        <v>0.6</v>
-      </c>
-      <c r="N57">
         <f t="shared" si="3"/>
         <v>0.25408618127786031</v>
       </c>
-      <c r="O57">
+      <c r="N57">
         <f t="shared" si="4"/>
         <v>0.26751592356687898</v>
       </c>
-      <c r="P57">
+      <c r="O57">
         <f t="shared" si="5"/>
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>1821</v>
+        <v>1366</v>
       </c>
       <c r="B58">
-        <v>1366</v>
+        <v>1280</v>
       </c>
       <c r="C58">
-        <v>1280</v>
+        <v>86</v>
       </c>
       <c r="D58">
-        <v>86</v>
+        <v>374</v>
       </c>
       <c r="E58">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="F58">
-        <v>370</v>
+        <v>4</v>
       </c>
       <c r="G58">
-        <v>4</v>
+        <v>332</v>
       </c>
       <c r="H58">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="I58">
-        <v>329</v>
+        <v>3</v>
       </c>
       <c r="J58">
-        <v>3</v>
+        <v>0.88770053475935828</v>
       </c>
       <c r="K58">
-        <v>0.88770053475935828</v>
+        <v>0.88918918918918921</v>
       </c>
       <c r="L58">
-        <v>0.88918918918918921</v>
+        <v>0.75</v>
       </c>
       <c r="M58">
-        <v>0.75</v>
-      </c>
-      <c r="N58">
         <f t="shared" si="3"/>
         <v>0.24304538799414349</v>
       </c>
-      <c r="O58">
+      <c r="N58">
         <f t="shared" si="4"/>
         <v>0.25703124999999999</v>
       </c>
-      <c r="P58">
+      <c r="O58">
         <f t="shared" si="5"/>
         <v>3.4883720930232558E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>1821</v>
+        <v>1374</v>
       </c>
       <c r="B59">
-        <v>1374</v>
+        <v>1285</v>
       </c>
       <c r="C59">
-        <v>1285</v>
+        <v>89</v>
       </c>
       <c r="D59">
-        <v>89</v>
+        <v>376</v>
       </c>
       <c r="E59">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="F59">
-        <v>365</v>
+        <v>11</v>
       </c>
       <c r="G59">
-        <v>11</v>
+        <v>339</v>
       </c>
       <c r="H59">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="I59">
-        <v>333</v>
+        <v>6</v>
       </c>
       <c r="J59">
-        <v>6</v>
+        <v>0.90159574468085102</v>
       </c>
       <c r="K59">
-        <v>0.90159574468085102</v>
+        <v>0.9123287671232877</v>
       </c>
       <c r="L59">
-        <v>0.9123287671232877</v>
+        <v>0.54545454545454541</v>
       </c>
       <c r="M59">
-        <v>0.54545454545454541</v>
-      </c>
-      <c r="N59">
         <f t="shared" si="3"/>
         <v>0.24672489082969432</v>
       </c>
-      <c r="O59">
+      <c r="N59">
         <f t="shared" si="4"/>
         <v>0.25914396887159535</v>
       </c>
-      <c r="P59">
+      <c r="O59">
         <f t="shared" si="5"/>
         <v>6.741573033707865E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>1821</v>
+        <v>1342</v>
       </c>
       <c r="B60">
-        <v>1342</v>
+        <v>1241</v>
       </c>
       <c r="C60">
-        <v>1241</v>
+        <v>101</v>
       </c>
       <c r="D60">
-        <v>101</v>
+        <v>339</v>
       </c>
       <c r="E60">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="F60">
-        <v>334</v>
+        <v>5</v>
       </c>
       <c r="G60">
-        <v>5</v>
+        <v>309</v>
       </c>
       <c r="H60">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I60">
-        <v>306</v>
+        <v>3</v>
       </c>
       <c r="J60">
-        <v>3</v>
+        <v>0.91150442477876104</v>
       </c>
       <c r="K60">
-        <v>0.91150442477876104</v>
+        <v>0.91616766467065869</v>
       </c>
       <c r="L60">
-        <v>0.91616766467065869</v>
+        <v>0.6</v>
       </c>
       <c r="M60">
-        <v>0.6</v>
-      </c>
-      <c r="N60">
         <f t="shared" si="3"/>
         <v>0.23025335320417287</v>
       </c>
-      <c r="O60">
+      <c r="N60">
         <f t="shared" si="4"/>
         <v>0.24657534246575341</v>
       </c>
-      <c r="P60">
+      <c r="O60">
         <f t="shared" si="5"/>
         <v>2.9702970297029702E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>1821</v>
+        <v>1373</v>
       </c>
       <c r="B61">
-        <v>1373</v>
+        <v>1263</v>
       </c>
       <c r="C61">
-        <v>1263</v>
+        <v>110</v>
       </c>
       <c r="D61">
-        <v>110</v>
+        <v>345</v>
       </c>
       <c r="E61">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="F61">
-        <v>336</v>
+        <v>9</v>
       </c>
       <c r="G61">
-        <v>9</v>
+        <v>313</v>
       </c>
       <c r="H61">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="I61">
-        <v>309</v>
+        <v>4</v>
       </c>
       <c r="J61">
-        <v>4</v>
+        <v>0.90724637681159426</v>
       </c>
       <c r="K61">
-        <v>0.90724637681159426</v>
+        <v>0.9196428571428571</v>
       </c>
       <c r="L61">
-        <v>0.9196428571428571</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="M61">
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="N61">
         <f t="shared" si="3"/>
         <v>0.22796795338674436</v>
       </c>
-      <c r="O61">
+      <c r="N61">
         <f t="shared" si="4"/>
         <v>0.24465558194774348</v>
       </c>
-      <c r="P61">
+      <c r="O61">
         <f t="shared" si="5"/>
         <v>3.6363636363636362E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>1821</v>
+        <v>1348</v>
       </c>
       <c r="B62">
-        <v>1348</v>
+        <v>1246</v>
       </c>
       <c r="C62">
-        <v>1246</v>
+        <v>102</v>
       </c>
       <c r="D62">
-        <v>102</v>
+        <v>348</v>
       </c>
       <c r="E62">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="F62">
-        <v>337</v>
+        <v>11</v>
       </c>
       <c r="G62">
-        <v>11</v>
+        <v>310</v>
       </c>
       <c r="H62">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="I62">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="J62">
-        <v>10</v>
+        <v>0.89080459770114939</v>
       </c>
       <c r="K62">
-        <v>0.89080459770114939</v>
+        <v>0.89020771513353114</v>
       </c>
       <c r="L62">
-        <v>0.89020771513353114</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="M62">
-        <v>0.90909090909090906</v>
-      </c>
-      <c r="N62">
         <f t="shared" si="3"/>
         <v>0.22997032640949555</v>
       </c>
-      <c r="O62">
+      <c r="N62">
         <f t="shared" si="4"/>
         <v>0.24077046548956663</v>
       </c>
-      <c r="P62">
+      <c r="O62">
         <f t="shared" si="5"/>
         <v>9.8039215686274508E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>1821</v>
+        <v>1364</v>
       </c>
       <c r="B63">
-        <v>1364</v>
+        <v>1275</v>
       </c>
       <c r="C63">
-        <v>1275</v>
+        <v>89</v>
       </c>
       <c r="D63">
-        <v>89</v>
+        <v>382</v>
       </c>
       <c r="E63">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="F63">
-        <v>376</v>
+        <v>6</v>
       </c>
       <c r="G63">
-        <v>6</v>
+        <v>351</v>
       </c>
       <c r="H63">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="I63">
-        <v>346</v>
+        <v>5</v>
       </c>
       <c r="J63">
-        <v>5</v>
+        <v>0.91884816753926701</v>
       </c>
       <c r="K63">
-        <v>0.91884816753926701</v>
+        <v>0.92021276595744683</v>
       </c>
       <c r="L63">
-        <v>0.92021276595744683</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="M63">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N63">
         <f t="shared" si="3"/>
         <v>0.25733137829912023</v>
       </c>
-      <c r="O63">
+      <c r="N63">
         <f t="shared" si="4"/>
         <v>0.27137254901960783</v>
       </c>
-      <c r="P63">
+      <c r="O63">
         <f t="shared" si="5"/>
         <v>5.6179775280898875E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>1821</v>
+        <v>1384</v>
       </c>
       <c r="B64">
-        <v>1384</v>
+        <v>1284</v>
       </c>
       <c r="C64">
-        <v>1284</v>
+        <v>100</v>
       </c>
       <c r="D64">
-        <v>100</v>
+        <v>343</v>
       </c>
       <c r="E64">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="F64">
-        <v>334</v>
+        <v>9</v>
       </c>
       <c r="G64">
-        <v>9</v>
+        <v>311</v>
       </c>
       <c r="H64">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="I64">
-        <v>305</v>
+        <v>6</v>
       </c>
       <c r="J64">
-        <v>6</v>
+        <v>0.90670553935860054</v>
       </c>
       <c r="K64">
-        <v>0.90670553935860054</v>
+        <v>0.91317365269461082</v>
       </c>
       <c r="L64">
-        <v>0.91317365269461082</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="M64">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="N64">
         <f t="shared" si="3"/>
         <v>0.22471098265895953</v>
       </c>
-      <c r="O64">
+      <c r="N64">
         <f t="shared" si="4"/>
         <v>0.23753894080996885</v>
       </c>
-      <c r="P64">
+      <c r="O64">
         <f t="shared" si="5"/>
         <v>0.06</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>1821</v>
+        <v>1376</v>
       </c>
       <c r="B65">
-        <v>1376</v>
+        <v>1279</v>
       </c>
       <c r="C65">
-        <v>1279</v>
+        <v>97</v>
       </c>
       <c r="D65">
-        <v>97</v>
+        <v>368</v>
       </c>
       <c r="E65">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="F65">
-        <v>349</v>
+        <v>19</v>
       </c>
       <c r="G65">
-        <v>19</v>
+        <v>335</v>
       </c>
       <c r="H65">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="I65">
-        <v>324</v>
+        <v>11</v>
       </c>
       <c r="J65">
-        <v>11</v>
+        <v>0.91032608695652173</v>
       </c>
       <c r="K65">
-        <v>0.91032608695652173</v>
+        <v>0.92836676217765046</v>
       </c>
       <c r="L65">
-        <v>0.92836676217765046</v>
+        <v>0.57894736842105265</v>
       </c>
       <c r="M65">
-        <v>0.57894736842105265</v>
-      </c>
-      <c r="N65">
         <f t="shared" si="3"/>
         <v>0.24345930232558138</v>
       </c>
-      <c r="O65">
+      <c r="N65">
         <f t="shared" si="4"/>
         <v>0.25332290852228301</v>
       </c>
-      <c r="P65">
+      <c r="O65">
         <f t="shared" si="5"/>
         <v>0.1134020618556701</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>1821</v>
+        <v>1368</v>
       </c>
       <c r="B66">
-        <v>1368</v>
+        <v>1261</v>
       </c>
       <c r="C66">
-        <v>1261</v>
+        <v>107</v>
       </c>
       <c r="D66">
-        <v>107</v>
+        <v>351</v>
       </c>
       <c r="E66">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F66">
-        <v>343</v>
+        <v>8</v>
       </c>
       <c r="G66">
-        <v>8</v>
+        <v>320</v>
       </c>
       <c r="H66">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="I66">
-        <v>315</v>
+        <v>5</v>
       </c>
       <c r="J66">
-        <v>5</v>
+        <v>0.9116809116809117</v>
       </c>
       <c r="K66">
-        <v>0.9116809116809117</v>
+        <v>0.91836734693877553</v>
       </c>
       <c r="L66">
-        <v>0.91836734693877553</v>
+        <v>0.625</v>
       </c>
       <c r="M66">
-        <v>0.625</v>
-      </c>
-      <c r="N66">
         <f t="shared" si="3"/>
         <v>0.23391812865497075</v>
       </c>
-      <c r="O66">
+      <c r="N66">
         <f t="shared" si="4"/>
         <v>0.24980174464710547</v>
       </c>
-      <c r="P66">
+      <c r="O66">
         <f t="shared" si="5"/>
         <v>4.6728971962616821E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>1821</v>
+        <v>1366</v>
       </c>
       <c r="B67">
-        <v>1366</v>
+        <v>1265</v>
       </c>
       <c r="C67">
-        <v>1265</v>
+        <v>101</v>
       </c>
       <c r="D67">
-        <v>101</v>
+        <v>324</v>
       </c>
       <c r="E67">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="F67">
-        <v>315</v>
+        <v>9</v>
       </c>
       <c r="G67">
-        <v>9</v>
+        <v>298</v>
       </c>
       <c r="H67">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="I67">
-        <v>290</v>
+        <v>8</v>
       </c>
       <c r="J67">
-        <v>8</v>
+        <v>0.91975308641975306</v>
       </c>
       <c r="K67">
-        <v>0.91975308641975306</v>
+        <v>0.92063492063492058</v>
       </c>
       <c r="L67">
-        <v>0.92063492063492058</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="M67">
-        <v>0.88888888888888884</v>
+        <f t="shared" ref="M67:M99" si="6">G67/A67</f>
+        <v>0.21815519765739386</v>
       </c>
       <c r="N67">
-        <f t="shared" ref="N67:N97" si="6">H67/B67</f>
-        <v>0.21815519765739386</v>
+        <f t="shared" ref="N67:N99" si="7">H67/B67</f>
+        <v>0.22924901185770752</v>
       </c>
       <c r="O67">
-        <f t="shared" ref="O67:O97" si="7">I67/C67</f>
-        <v>0.22924901185770752</v>
-      </c>
-      <c r="P67">
-        <f t="shared" ref="P67:P97" si="8">J67/D67</f>
+        <f t="shared" ref="O67:O99" si="8">I67/C67</f>
         <v>7.9207920792079209E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>1821</v>
+        <v>1356</v>
       </c>
       <c r="B68">
-        <v>1356</v>
+        <v>1249</v>
       </c>
       <c r="C68">
-        <v>1249</v>
+        <v>107</v>
       </c>
       <c r="D68">
-        <v>107</v>
+        <v>334</v>
       </c>
       <c r="E68">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="F68">
-        <v>327</v>
+        <v>7</v>
       </c>
       <c r="G68">
-        <v>7</v>
+        <v>303</v>
       </c>
       <c r="H68">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="I68">
-        <v>297</v>
+        <v>6</v>
       </c>
       <c r="J68">
-        <v>6</v>
+        <v>0.90718562874251496</v>
       </c>
       <c r="K68">
-        <v>0.90718562874251496</v>
+        <v>0.90825688073394495</v>
       </c>
       <c r="L68">
-        <v>0.90825688073394495</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="M68">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="N68">
         <f t="shared" si="6"/>
         <v>0.22345132743362831</v>
       </c>
-      <c r="O68">
+      <c r="N68">
         <f t="shared" si="7"/>
         <v>0.2377902321857486</v>
       </c>
-      <c r="P68">
+      <c r="O68">
         <f t="shared" si="8"/>
         <v>5.6074766355140186E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>1821</v>
+        <v>1324</v>
       </c>
       <c r="B69">
-        <v>1324</v>
+        <v>1229</v>
       </c>
       <c r="C69">
-        <v>1229</v>
+        <v>95</v>
       </c>
       <c r="D69">
-        <v>95</v>
+        <v>361</v>
       </c>
       <c r="E69">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="F69">
-        <v>351</v>
+        <v>10</v>
       </c>
       <c r="G69">
-        <v>10</v>
+        <v>327</v>
       </c>
       <c r="H69">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="I69">
-        <v>320</v>
+        <v>7</v>
       </c>
       <c r="J69">
-        <v>7</v>
+        <v>0.90581717451523547</v>
       </c>
       <c r="K69">
-        <v>0.90581717451523547</v>
+        <v>0.9116809116809117</v>
       </c>
       <c r="L69">
-        <v>0.9116809116809117</v>
+        <v>0.7</v>
       </c>
       <c r="M69">
-        <v>0.7</v>
-      </c>
-      <c r="N69">
         <f t="shared" si="6"/>
         <v>0.24697885196374622</v>
       </c>
-      <c r="O69">
+      <c r="N69">
         <f t="shared" si="7"/>
         <v>0.26037428803905616</v>
       </c>
-      <c r="P69">
+      <c r="O69">
         <f t="shared" si="8"/>
         <v>7.3684210526315783E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>1821</v>
+        <v>1371</v>
       </c>
       <c r="B70">
-        <v>1371</v>
+        <v>1278</v>
       </c>
       <c r="C70">
-        <v>1278</v>
+        <v>93</v>
       </c>
       <c r="D70">
-        <v>93</v>
+        <v>365</v>
       </c>
       <c r="E70">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="F70">
-        <v>354</v>
+        <v>11</v>
       </c>
       <c r="G70">
-        <v>11</v>
+        <v>321</v>
       </c>
       <c r="H70">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="I70">
-        <v>314</v>
+        <v>7</v>
       </c>
       <c r="J70">
-        <v>7</v>
+        <v>0.8794520547945206</v>
       </c>
       <c r="K70">
-        <v>0.8794520547945206</v>
+        <v>0.88700564971751417</v>
       </c>
       <c r="L70">
-        <v>0.88700564971751417</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="M70">
-        <v>0.63636363636363635</v>
-      </c>
-      <c r="N70">
         <f t="shared" si="6"/>
         <v>0.23413566739606126</v>
       </c>
-      <c r="O70">
+      <c r="N70">
         <f t="shared" si="7"/>
         <v>0.24569640062597808</v>
       </c>
-      <c r="P70">
+      <c r="O70">
         <f t="shared" si="8"/>
         <v>7.5268817204301078E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>1821</v>
+        <v>1337</v>
       </c>
       <c r="B71">
-        <v>1337</v>
+        <v>1235</v>
       </c>
       <c r="C71">
-        <v>1235</v>
+        <v>102</v>
       </c>
       <c r="D71">
-        <v>102</v>
+        <v>354</v>
       </c>
       <c r="E71">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="F71">
-        <v>346</v>
+        <v>8</v>
       </c>
       <c r="G71">
-        <v>8</v>
+        <v>328</v>
       </c>
       <c r="H71">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="I71">
-        <v>321</v>
+        <v>7</v>
       </c>
       <c r="J71">
-        <v>7</v>
+        <v>0.92655367231638419</v>
       </c>
       <c r="K71">
-        <v>0.92655367231638419</v>
+        <v>0.9277456647398844</v>
       </c>
       <c r="L71">
-        <v>0.9277456647398844</v>
+        <v>0.875</v>
       </c>
       <c r="M71">
-        <v>0.875</v>
-      </c>
-      <c r="N71">
         <f t="shared" si="6"/>
         <v>0.24532535527299926</v>
       </c>
-      <c r="O71">
+      <c r="N71">
         <f t="shared" si="7"/>
         <v>0.25991902834008096</v>
       </c>
-      <c r="P71">
+      <c r="O71">
         <f t="shared" si="8"/>
         <v>6.8627450980392163E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>1821</v>
+        <v>1345</v>
       </c>
       <c r="B72">
-        <v>1345</v>
+        <v>1233</v>
       </c>
       <c r="C72">
-        <v>1233</v>
+        <v>112</v>
       </c>
       <c r="D72">
-        <v>112</v>
+        <v>330</v>
       </c>
       <c r="E72">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="F72">
-        <v>325</v>
+        <v>5</v>
       </c>
       <c r="G72">
-        <v>5</v>
+        <v>298</v>
       </c>
       <c r="H72">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I72">
-        <v>295</v>
+        <v>3</v>
       </c>
       <c r="J72">
-        <v>3</v>
+        <v>0.90303030303030307</v>
       </c>
       <c r="K72">
-        <v>0.90303030303030307</v>
+        <v>0.90769230769230769</v>
       </c>
       <c r="L72">
-        <v>0.90769230769230769</v>
+        <v>0.6</v>
       </c>
       <c r="M72">
-        <v>0.6</v>
-      </c>
-      <c r="N72">
         <f t="shared" si="6"/>
         <v>0.22156133828996283</v>
       </c>
-      <c r="O72">
+      <c r="N72">
         <f t="shared" si="7"/>
         <v>0.23925385239253852</v>
       </c>
-      <c r="P72">
+      <c r="O72">
         <f t="shared" si="8"/>
         <v>2.6785714285714284E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>1821</v>
+        <v>1341</v>
       </c>
       <c r="B73">
-        <v>1341</v>
+        <v>1264</v>
       </c>
       <c r="C73">
-        <v>1264</v>
+        <v>77</v>
       </c>
       <c r="D73">
-        <v>77</v>
+        <v>392</v>
       </c>
       <c r="E73">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="F73">
-        <v>383</v>
+        <v>9</v>
       </c>
       <c r="G73">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="H73">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="I73">
-        <v>350</v>
+        <v>7</v>
       </c>
       <c r="J73">
-        <v>7</v>
+        <v>0.9107142857142857</v>
       </c>
       <c r="K73">
-        <v>0.9107142857142857</v>
+        <v>0.91383812010443866</v>
       </c>
       <c r="L73">
-        <v>0.91383812010443866</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="M73">
-        <v>0.77777777777777779</v>
-      </c>
-      <c r="N73">
         <f t="shared" si="6"/>
         <v>0.26621923937360181</v>
       </c>
-      <c r="O73">
+      <c r="N73">
         <f t="shared" si="7"/>
         <v>0.27689873417721517</v>
       </c>
-      <c r="P73">
+      <c r="O73">
         <f t="shared" si="8"/>
         <v>9.0909090909090912E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>1821</v>
+        <v>1370</v>
       </c>
       <c r="B74">
-        <v>1370</v>
+        <v>1262</v>
       </c>
       <c r="C74">
-        <v>1262</v>
+        <v>108</v>
       </c>
       <c r="D74">
-        <v>108</v>
+        <v>321</v>
       </c>
       <c r="E74">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F74">
-        <v>315</v>
+        <v>6</v>
       </c>
       <c r="G74">
-        <v>6</v>
+        <v>280</v>
       </c>
       <c r="H74">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I74">
-        <v>278</v>
+        <v>2</v>
       </c>
       <c r="J74">
-        <v>2</v>
+        <v>0.87227414330218067</v>
       </c>
       <c r="K74">
-        <v>0.87227414330218067</v>
+        <v>0.88253968253968251</v>
       </c>
       <c r="L74">
-        <v>0.88253968253968251</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="M74">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="N74">
         <f t="shared" si="6"/>
         <v>0.20437956204379562</v>
       </c>
-      <c r="O74">
+      <c r="N74">
         <f t="shared" si="7"/>
         <v>0.2202852614896989</v>
       </c>
-      <c r="P74">
+      <c r="O74">
         <f t="shared" si="8"/>
         <v>1.8518518518518517E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>1821</v>
+        <v>1347</v>
       </c>
       <c r="B75">
-        <v>1347</v>
+        <v>1253</v>
       </c>
       <c r="C75">
-        <v>1253</v>
+        <v>94</v>
       </c>
       <c r="D75">
-        <v>94</v>
+        <v>371</v>
       </c>
       <c r="E75">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="F75">
-        <v>361</v>
+        <v>10</v>
       </c>
       <c r="G75">
-        <v>10</v>
+        <v>340</v>
       </c>
       <c r="H75">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="I75">
-        <v>331</v>
+        <v>9</v>
       </c>
       <c r="J75">
-        <v>9</v>
+        <v>0.9164420485175202</v>
       </c>
       <c r="K75">
-        <v>0.9164420485175202</v>
+        <v>0.91689750692520777</v>
       </c>
       <c r="L75">
-        <v>0.91689750692520777</v>
+        <v>0.9</v>
       </c>
       <c r="M75">
-        <v>0.9</v>
-      </c>
-      <c r="N75">
         <f t="shared" si="6"/>
         <v>0.2524127691165553</v>
       </c>
-      <c r="O75">
+      <c r="N75">
         <f t="shared" si="7"/>
         <v>0.26416600159616921</v>
       </c>
-      <c r="P75">
+      <c r="O75">
         <f t="shared" si="8"/>
         <v>9.5744680851063829E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>1821</v>
+        <v>1359</v>
       </c>
       <c r="B76">
-        <v>1359</v>
+        <v>1266</v>
       </c>
       <c r="C76">
-        <v>1266</v>
+        <v>93</v>
       </c>
       <c r="D76">
-        <v>93</v>
+        <v>355</v>
       </c>
       <c r="E76">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="F76">
-        <v>341</v>
+        <v>14</v>
       </c>
       <c r="G76">
-        <v>14</v>
+        <v>326</v>
       </c>
       <c r="H76">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="I76">
-        <v>316</v>
+        <v>10</v>
       </c>
       <c r="J76">
-        <v>10</v>
+        <v>0.91830985915492958</v>
       </c>
       <c r="K76">
-        <v>0.91830985915492958</v>
+        <v>0.92668621700879761</v>
       </c>
       <c r="L76">
-        <v>0.92668621700879761</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="M76">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="N76">
         <f t="shared" si="6"/>
         <v>0.23988226637233259</v>
       </c>
-      <c r="O76">
+      <c r="N76">
         <f t="shared" si="7"/>
         <v>0.24960505529225907</v>
       </c>
-      <c r="P76">
+      <c r="O76">
         <f t="shared" si="8"/>
         <v>0.10752688172043011</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>1821</v>
+        <v>1347</v>
       </c>
       <c r="B77">
-        <v>1347</v>
+        <v>1242</v>
       </c>
       <c r="C77">
-        <v>1242</v>
+        <v>105</v>
       </c>
       <c r="D77">
-        <v>105</v>
+        <v>356</v>
       </c>
       <c r="E77">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="F77">
-        <v>352</v>
+        <v>4</v>
       </c>
       <c r="G77">
+        <v>323</v>
+      </c>
+      <c r="H77">
+        <v>319</v>
+      </c>
+      <c r="I77">
         <v>4</v>
       </c>
-      <c r="H77">
-        <v>323</v>
-      </c>
-      <c r="I77">
-        <v>319</v>
-      </c>
       <c r="J77">
-        <v>4</v>
+        <v>0.90730337078651691</v>
       </c>
       <c r="K77">
-        <v>0.90730337078651691</v>
+        <v>0.90625</v>
       </c>
       <c r="L77">
-        <v>0.90625</v>
+        <v>1</v>
       </c>
       <c r="M77">
-        <v>1</v>
-      </c>
-      <c r="N77">
         <f t="shared" si="6"/>
         <v>0.23979213066072755</v>
       </c>
-      <c r="O77">
+      <c r="N77">
         <f t="shared" si="7"/>
         <v>0.25684380032206117</v>
       </c>
-      <c r="P77">
+      <c r="O77">
         <f t="shared" si="8"/>
         <v>3.8095238095238099E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>1821</v>
+        <v>1368</v>
       </c>
       <c r="B78">
-        <v>1368</v>
+        <v>1272</v>
       </c>
       <c r="C78">
-        <v>1272</v>
+        <v>96</v>
       </c>
       <c r="D78">
-        <v>96</v>
+        <v>375</v>
       </c>
       <c r="E78">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="F78">
-        <v>364</v>
+        <v>11</v>
       </c>
       <c r="G78">
-        <v>11</v>
+        <v>344</v>
       </c>
       <c r="H78">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="I78">
-        <v>337</v>
+        <v>7</v>
       </c>
       <c r="J78">
-        <v>7</v>
+        <v>0.91733333333333333</v>
       </c>
       <c r="K78">
-        <v>0.91733333333333333</v>
+        <v>0.92582417582417587</v>
       </c>
       <c r="L78">
-        <v>0.92582417582417587</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="M78">
-        <v>0.63636363636363635</v>
-      </c>
-      <c r="N78">
         <f t="shared" si="6"/>
         <v>0.25146198830409355</v>
       </c>
-      <c r="O78">
+      <c r="N78">
         <f t="shared" si="7"/>
         <v>0.26493710691823902</v>
       </c>
-      <c r="P78">
+      <c r="O78">
         <f t="shared" si="8"/>
         <v>7.2916666666666671E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>1821</v>
+        <v>1361</v>
       </c>
       <c r="B79">
-        <v>1361</v>
+        <v>1263</v>
       </c>
       <c r="C79">
-        <v>1263</v>
+        <v>98</v>
       </c>
       <c r="D79">
-        <v>98</v>
+        <v>359</v>
       </c>
       <c r="E79">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="F79">
-        <v>349</v>
+        <v>10</v>
       </c>
       <c r="G79">
-        <v>10</v>
+        <v>326</v>
       </c>
       <c r="H79">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="I79">
-        <v>321</v>
+        <v>5</v>
       </c>
       <c r="J79">
-        <v>5</v>
+        <v>0.9080779944289693</v>
       </c>
       <c r="K79">
-        <v>0.9080779944289693</v>
+        <v>0.91977077363896853</v>
       </c>
       <c r="L79">
-        <v>0.91977077363896853</v>
+        <v>0.5</v>
       </c>
       <c r="M79">
-        <v>0.5</v>
-      </c>
-      <c r="N79">
         <f t="shared" si="6"/>
         <v>0.23952975753122704</v>
       </c>
-      <c r="O79">
+      <c r="N79">
         <f t="shared" si="7"/>
         <v>0.25415676959619954</v>
       </c>
-      <c r="P79">
+      <c r="O79">
         <f t="shared" si="8"/>
         <v>5.1020408163265307E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>1821</v>
+        <v>1352</v>
       </c>
       <c r="B80">
-        <v>1352</v>
+        <v>1246</v>
       </c>
       <c r="C80">
-        <v>1246</v>
+        <v>106</v>
       </c>
       <c r="D80">
-        <v>106</v>
+        <v>372</v>
       </c>
       <c r="E80">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="F80">
-        <v>354</v>
+        <v>18</v>
       </c>
       <c r="G80">
-        <v>18</v>
+        <v>324</v>
       </c>
       <c r="H80">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="I80">
-        <v>312</v>
+        <v>12</v>
       </c>
       <c r="J80">
-        <v>12</v>
+        <v>0.87096774193548387</v>
       </c>
       <c r="K80">
-        <v>0.87096774193548387</v>
+        <v>0.88135593220338981</v>
       </c>
       <c r="L80">
-        <v>0.88135593220338981</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="M80">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="N80">
         <f t="shared" si="6"/>
         <v>0.23964497041420119</v>
       </c>
-      <c r="O80">
+      <c r="N80">
         <f t="shared" si="7"/>
         <v>0.2504012841091493</v>
       </c>
-      <c r="P80">
+      <c r="O80">
         <f t="shared" si="8"/>
         <v>0.11320754716981132</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>1821</v>
+        <v>1330</v>
       </c>
       <c r="B81">
-        <v>1330</v>
+        <v>1228</v>
       </c>
       <c r="C81">
-        <v>1228</v>
+        <v>102</v>
       </c>
       <c r="D81">
-        <v>102</v>
+        <v>340</v>
       </c>
       <c r="E81">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="F81">
-        <v>334</v>
+        <v>6</v>
       </c>
       <c r="G81">
-        <v>6</v>
+        <v>314</v>
       </c>
       <c r="H81">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="I81">
-        <v>309</v>
+        <v>5</v>
       </c>
       <c r="J81">
-        <v>5</v>
+        <v>0.92352941176470593</v>
       </c>
       <c r="K81">
-        <v>0.92352941176470593</v>
+        <v>0.92514970059880242</v>
       </c>
       <c r="L81">
-        <v>0.92514970059880242</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="M81">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N81">
         <f t="shared" si="6"/>
         <v>0.23609022556390977</v>
       </c>
-      <c r="O81">
+      <c r="N81">
         <f t="shared" si="7"/>
         <v>0.25162866449511401</v>
       </c>
-      <c r="P81">
+      <c r="O81">
         <f t="shared" si="8"/>
         <v>4.9019607843137254E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>1821</v>
+        <v>1386</v>
       </c>
       <c r="B82">
-        <v>1386</v>
+        <v>1300</v>
       </c>
       <c r="C82">
-        <v>1300</v>
+        <v>86</v>
       </c>
       <c r="D82">
-        <v>86</v>
+        <v>377</v>
       </c>
       <c r="E82">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="F82">
-        <v>368</v>
+        <v>9</v>
       </c>
       <c r="G82">
-        <v>9</v>
+        <v>341</v>
       </c>
       <c r="H82">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="I82">
-        <v>336</v>
+        <v>5</v>
       </c>
       <c r="J82">
-        <v>5</v>
+        <v>0.9045092838196287</v>
       </c>
       <c r="K82">
-        <v>0.9045092838196287</v>
+        <v>0.91304347826086951</v>
       </c>
       <c r="L82">
-        <v>0.91304347826086951</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="M82">
-        <v>0.55555555555555558</v>
-      </c>
-      <c r="N82">
         <f t="shared" si="6"/>
         <v>0.24603174603174602</v>
       </c>
-      <c r="O82">
+      <c r="N82">
         <f t="shared" si="7"/>
         <v>0.25846153846153846</v>
       </c>
-      <c r="P82">
+      <c r="O82">
         <f t="shared" si="8"/>
         <v>5.8139534883720929E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>1821</v>
+        <v>1387</v>
       </c>
       <c r="B83">
-        <v>1387</v>
+        <v>1287</v>
       </c>
       <c r="C83">
-        <v>1287</v>
+        <v>100</v>
       </c>
       <c r="D83">
-        <v>100</v>
+        <v>335</v>
       </c>
       <c r="E83">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="F83">
-        <v>326</v>
+        <v>9</v>
       </c>
       <c r="G83">
-        <v>9</v>
+        <v>307</v>
       </c>
       <c r="H83">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="I83">
-        <v>301</v>
+        <v>6</v>
       </c>
       <c r="J83">
-        <v>6</v>
+        <v>0.91641791044776122</v>
       </c>
       <c r="K83">
-        <v>0.91641791044776122</v>
+        <v>0.92331288343558282</v>
       </c>
       <c r="L83">
-        <v>0.92331288343558282</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="M83">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="N83">
         <f t="shared" si="6"/>
         <v>0.22134102379235759</v>
       </c>
-      <c r="O83">
+      <c r="N83">
         <f t="shared" si="7"/>
         <v>0.23387723387723389</v>
       </c>
-      <c r="P83">
+      <c r="O83">
         <f t="shared" si="8"/>
         <v>0.06</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>1821</v>
+        <v>1362</v>
       </c>
       <c r="B84">
-        <v>1362</v>
+        <v>1258</v>
       </c>
       <c r="C84">
-        <v>1258</v>
+        <v>104</v>
       </c>
       <c r="D84">
-        <v>104</v>
+        <v>394</v>
       </c>
       <c r="E84">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="F84">
-        <v>386</v>
+        <v>8</v>
       </c>
       <c r="G84">
-        <v>8</v>
+        <v>348</v>
       </c>
       <c r="H84">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="I84">
-        <v>343</v>
+        <v>5</v>
       </c>
       <c r="J84">
-        <v>5</v>
+        <v>0.88324873096446699</v>
       </c>
       <c r="K84">
-        <v>0.88324873096446699</v>
+        <v>0.8886010362694301</v>
       </c>
       <c r="L84">
-        <v>0.8886010362694301</v>
+        <v>0.625</v>
       </c>
       <c r="M84">
-        <v>0.625</v>
-      </c>
-      <c r="N84">
         <f t="shared" si="6"/>
         <v>0.25550660792951541</v>
       </c>
-      <c r="O84">
+      <c r="N84">
         <f t="shared" si="7"/>
         <v>0.27265500794912562</v>
       </c>
-      <c r="P84">
+      <c r="O84">
         <f t="shared" si="8"/>
         <v>4.807692307692308E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>1821</v>
+        <v>1361</v>
       </c>
       <c r="B85">
-        <v>1361</v>
+        <v>1262</v>
       </c>
       <c r="C85">
-        <v>1262</v>
+        <v>99</v>
       </c>
       <c r="D85">
-        <v>99</v>
+        <v>375</v>
       </c>
       <c r="E85">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="F85">
-        <v>369</v>
+        <v>6</v>
       </c>
       <c r="G85">
-        <v>6</v>
+        <v>331</v>
       </c>
       <c r="H85">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I85">
-        <v>327</v>
+        <v>4</v>
       </c>
       <c r="J85">
-        <v>4</v>
+        <v>0.88266666666666671</v>
       </c>
       <c r="K85">
-        <v>0.88266666666666671</v>
+        <v>0.88617886178861793</v>
       </c>
       <c r="L85">
-        <v>0.88617886178861793</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="M85">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="N85">
         <f t="shared" si="6"/>
         <v>0.24320352681851579</v>
       </c>
-      <c r="O85">
+      <c r="N85">
         <f t="shared" si="7"/>
         <v>0.25911251980982569</v>
       </c>
-      <c r="P85">
+      <c r="O85">
         <f t="shared" si="8"/>
         <v>4.0404040404040407E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>1821</v>
+        <v>1357</v>
       </c>
       <c r="B86">
-        <v>1357</v>
+        <v>1265</v>
       </c>
       <c r="C86">
-        <v>1265</v>
+        <v>92</v>
       </c>
       <c r="D86">
-        <v>92</v>
+        <v>391</v>
       </c>
       <c r="E86">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="F86">
-        <v>379</v>
+        <v>12</v>
       </c>
       <c r="G86">
-        <v>12</v>
+        <v>346</v>
       </c>
       <c r="H86">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="I86">
-        <v>338</v>
+        <v>8</v>
       </c>
       <c r="J86">
-        <v>8</v>
+        <v>0.88491048593350385</v>
       </c>
       <c r="K86">
-        <v>0.88491048593350385</v>
+        <v>0.89182058047493407</v>
       </c>
       <c r="L86">
-        <v>0.89182058047493407</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="M86">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="N86">
         <f t="shared" si="6"/>
         <v>0.25497420781134855</v>
       </c>
-      <c r="O86">
+      <c r="N86">
         <f t="shared" si="7"/>
         <v>0.26719367588932808</v>
       </c>
-      <c r="P86">
+      <c r="O86">
         <f t="shared" si="8"/>
         <v>8.6956521739130432E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>1821</v>
+        <v>1326</v>
       </c>
       <c r="B87">
-        <v>1326</v>
+        <v>1210</v>
       </c>
       <c r="C87">
-        <v>1210</v>
+        <v>116</v>
       </c>
       <c r="D87">
-        <v>116</v>
+        <v>347</v>
       </c>
       <c r="E87">
-        <v>347</v>
+        <v>331</v>
       </c>
       <c r="F87">
-        <v>331</v>
+        <v>16</v>
       </c>
       <c r="G87">
-        <v>16</v>
+        <v>308</v>
       </c>
       <c r="H87">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="I87">
-        <v>298</v>
+        <v>10</v>
       </c>
       <c r="J87">
-        <v>10</v>
+        <v>0.88760806916426516</v>
       </c>
       <c r="K87">
-        <v>0.88760806916426516</v>
+        <v>0.90030211480362543</v>
       </c>
       <c r="L87">
-        <v>0.90030211480362543</v>
+        <v>0.625</v>
       </c>
       <c r="M87">
-        <v>0.625</v>
-      </c>
-      <c r="N87">
         <f t="shared" si="6"/>
         <v>0.23227752639517346</v>
       </c>
-      <c r="O87">
+      <c r="N87">
         <f t="shared" si="7"/>
         <v>0.24628099173553719</v>
       </c>
-      <c r="P87">
+      <c r="O87">
         <f t="shared" si="8"/>
         <v>8.6206896551724144E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>1821</v>
+        <v>1370</v>
       </c>
       <c r="B88">
-        <v>1370</v>
+        <v>1270</v>
       </c>
       <c r="C88">
-        <v>1270</v>
+        <v>100</v>
       </c>
       <c r="D88">
-        <v>100</v>
+        <v>333</v>
       </c>
       <c r="E88">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="F88">
-        <v>328</v>
+        <v>5</v>
       </c>
       <c r="G88">
-        <v>5</v>
+        <v>305</v>
       </c>
       <c r="H88">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I88">
-        <v>301</v>
+        <v>4</v>
       </c>
       <c r="J88">
-        <v>4</v>
+        <v>0.91591591591591592</v>
       </c>
       <c r="K88">
-        <v>0.91591591591591592</v>
+        <v>0.91768292682926833</v>
       </c>
       <c r="L88">
-        <v>0.91768292682926833</v>
+        <v>0.8</v>
       </c>
       <c r="M88">
-        <v>0.8</v>
-      </c>
-      <c r="N88">
         <f t="shared" si="6"/>
         <v>0.22262773722627738</v>
       </c>
-      <c r="O88">
+      <c r="N88">
         <f t="shared" si="7"/>
         <v>0.23700787401574802</v>
       </c>
-      <c r="P88">
+      <c r="O88">
         <f t="shared" si="8"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>1821</v>
+        <v>1358</v>
       </c>
       <c r="B89">
-        <v>1358</v>
+        <v>1270</v>
       </c>
       <c r="C89">
-        <v>1270</v>
+        <v>88</v>
       </c>
       <c r="D89">
-        <v>88</v>
+        <v>381</v>
       </c>
       <c r="E89">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="F89">
-        <v>375</v>
+        <v>6</v>
       </c>
       <c r="G89">
-        <v>6</v>
+        <v>348</v>
       </c>
       <c r="H89">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="I89">
-        <v>343</v>
+        <v>5</v>
       </c>
       <c r="J89">
-        <v>5</v>
+        <v>0.91338582677165359</v>
       </c>
       <c r="K89">
-        <v>0.91338582677165359</v>
+        <v>0.91466666666666663</v>
       </c>
       <c r="L89">
-        <v>0.91466666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="M89">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N89">
         <f t="shared" si="6"/>
         <v>0.25625920471281294</v>
       </c>
-      <c r="O89">
+      <c r="N89">
         <f t="shared" si="7"/>
         <v>0.27007874015748029</v>
       </c>
-      <c r="P89">
+      <c r="O89">
         <f t="shared" si="8"/>
         <v>5.6818181818181816E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>4552</v>
+        <v>1355</v>
       </c>
       <c r="B90">
-        <v>3707</v>
+        <v>1256</v>
       </c>
       <c r="C90">
-        <v>3506</v>
+        <v>99</v>
       </c>
       <c r="D90">
-        <v>201</v>
+        <v>363</v>
       </c>
       <c r="E90">
-        <v>925</v>
+        <v>354</v>
       </c>
       <c r="F90">
-        <v>900</v>
+        <v>9</v>
       </c>
       <c r="G90">
-        <v>25</v>
+        <v>319</v>
       </c>
       <c r="H90">
-        <v>861</v>
+        <v>315</v>
       </c>
       <c r="I90">
-        <v>841</v>
+        <v>4</v>
       </c>
       <c r="J90">
-        <v>20</v>
+        <v>0.87878787878787878</v>
       </c>
       <c r="K90">
-        <v>0.93081081081081085</v>
+        <v>0.88983050847457623</v>
       </c>
       <c r="L90">
-        <v>0.93444444444444441</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="M90">
-        <v>0.8</v>
+        <f t="shared" si="6"/>
+        <v>0.23542435424354244</v>
       </c>
       <c r="N90">
+        <f t="shared" si="7"/>
+        <v>0.25079617834394907</v>
+      </c>
+      <c r="O90">
+        <f t="shared" si="8"/>
+        <v>4.0404040404040407E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>1344</v>
+      </c>
+      <c r="B91">
+        <v>1245</v>
+      </c>
+      <c r="C91">
+        <v>99</v>
+      </c>
+      <c r="D91">
+        <v>348</v>
+      </c>
+      <c r="E91">
+        <v>334</v>
+      </c>
+      <c r="F91">
+        <v>14</v>
+      </c>
+      <c r="G91">
+        <v>307</v>
+      </c>
+      <c r="H91">
+        <v>299</v>
+      </c>
+      <c r="I91">
+        <v>8</v>
+      </c>
+      <c r="J91">
+        <v>0.88218390804597702</v>
+      </c>
+      <c r="K91">
+        <v>0.89520958083832336</v>
+      </c>
+      <c r="L91">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="M91">
         <f t="shared" si="6"/>
-        <v>0.23226328567574858</v>
-      </c>
-      <c r="O90">
+        <v>0.22842261904761904</v>
+      </c>
+      <c r="N91">
         <f t="shared" si="7"/>
-        <v>0.23987450085567599</v>
-      </c>
-      <c r="P90">
+        <v>0.24016064257028114</v>
+      </c>
+      <c r="O91">
         <f t="shared" si="8"/>
-        <v>9.950248756218906E-2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A91">
-        <v>4552</v>
-      </c>
-      <c r="B91">
-        <v>3707</v>
-      </c>
-      <c r="C91">
-        <v>3506</v>
-      </c>
-      <c r="D91">
-        <v>201</v>
-      </c>
-      <c r="E91">
-        <v>925</v>
-      </c>
-      <c r="F91">
-        <v>900</v>
-      </c>
-      <c r="G91">
-        <v>25</v>
-      </c>
-      <c r="H91">
-        <v>861</v>
-      </c>
-      <c r="I91">
-        <v>841</v>
-      </c>
-      <c r="J91">
-        <v>20</v>
-      </c>
-      <c r="K91">
-        <v>0.93081081081081085</v>
-      </c>
-      <c r="L91">
-        <v>0.93444444444444441</v>
-      </c>
-      <c r="M91">
-        <v>0.8</v>
-      </c>
-      <c r="N91">
+        <v>8.0808080808080815E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>1356</v>
+      </c>
+      <c r="B92">
+        <v>1253</v>
+      </c>
+      <c r="C92">
+        <v>103</v>
+      </c>
+      <c r="D92">
+        <v>329</v>
+      </c>
+      <c r="E92">
+        <v>319</v>
+      </c>
+      <c r="F92">
+        <v>10</v>
+      </c>
+      <c r="G92">
+        <v>303</v>
+      </c>
+      <c r="H92">
+        <v>296</v>
+      </c>
+      <c r="I92">
+        <v>7</v>
+      </c>
+      <c r="J92">
+        <v>0.92097264437689974</v>
+      </c>
+      <c r="K92">
+        <v>0.92789968652037613</v>
+      </c>
+      <c r="L92">
+        <v>0.7</v>
+      </c>
+      <c r="M92">
         <f t="shared" si="6"/>
-        <v>0.23226328567574858</v>
-      </c>
-      <c r="O91">
+        <v>0.22345132743362831</v>
+      </c>
+      <c r="N92">
         <f t="shared" si="7"/>
-        <v>0.23987450085567599</v>
-      </c>
-      <c r="P91">
+        <v>0.23623304070231443</v>
+      </c>
+      <c r="O92">
         <f t="shared" si="8"/>
-        <v>9.950248756218906E-2</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A92">
-        <v>4552</v>
-      </c>
-      <c r="B92">
-        <v>3707</v>
-      </c>
-      <c r="C92">
-        <v>3506</v>
-      </c>
-      <c r="D92">
-        <v>201</v>
-      </c>
-      <c r="E92">
-        <v>925</v>
-      </c>
-      <c r="F92">
-        <v>900</v>
-      </c>
-      <c r="G92">
-        <v>25</v>
-      </c>
-      <c r="H92">
-        <v>861</v>
-      </c>
-      <c r="I92">
-        <v>841</v>
-      </c>
-      <c r="J92">
-        <v>20</v>
-      </c>
-      <c r="K92">
-        <v>0.93081081081081085</v>
-      </c>
-      <c r="L92">
-        <v>0.93444444444444441</v>
-      </c>
-      <c r="M92">
-        <v>0.8</v>
-      </c>
-      <c r="N92">
+        <v>6.7961165048543687E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>1361</v>
+      </c>
+      <c r="B93">
+        <v>1250</v>
+      </c>
+      <c r="C93">
+        <v>111</v>
+      </c>
+      <c r="D93">
+        <v>359</v>
+      </c>
+      <c r="E93">
+        <v>340</v>
+      </c>
+      <c r="F93">
+        <v>19</v>
+      </c>
+      <c r="G93">
+        <v>316</v>
+      </c>
+      <c r="H93">
+        <v>306</v>
+      </c>
+      <c r="I93">
+        <v>10</v>
+      </c>
+      <c r="J93">
+        <v>0.88022284122562677</v>
+      </c>
+      <c r="K93">
+        <v>0.9</v>
+      </c>
+      <c r="L93">
+        <v>0.52631578947368418</v>
+      </c>
+      <c r="M93">
         <f t="shared" si="6"/>
-        <v>0.23226328567574858</v>
-      </c>
-      <c r="O92">
+        <v>0.23218221895664953</v>
+      </c>
+      <c r="N93">
         <f t="shared" si="7"/>
-        <v>0.23987450085567599</v>
-      </c>
-      <c r="P92">
+        <v>0.24479999999999999</v>
+      </c>
+      <c r="O93">
         <f t="shared" si="8"/>
-        <v>9.950248756218906E-2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A93">
-        <v>4552</v>
-      </c>
-      <c r="B93">
-        <v>3707</v>
-      </c>
-      <c r="C93">
-        <v>3506</v>
-      </c>
-      <c r="D93">
-        <v>201</v>
-      </c>
-      <c r="E93">
-        <v>925</v>
-      </c>
-      <c r="F93">
-        <v>900</v>
-      </c>
-      <c r="G93">
-        <v>25</v>
-      </c>
-      <c r="H93">
-        <v>861</v>
-      </c>
-      <c r="I93">
-        <v>841</v>
-      </c>
-      <c r="J93">
-        <v>20</v>
-      </c>
-      <c r="K93">
-        <v>0.93081081081081085</v>
-      </c>
-      <c r="L93">
-        <v>0.93444444444444441</v>
-      </c>
-      <c r="M93">
-        <v>0.8</v>
-      </c>
-      <c r="N93">
+        <v>9.0090090090090086E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>1361</v>
+      </c>
+      <c r="B94">
+        <v>1267</v>
+      </c>
+      <c r="C94">
+        <v>94</v>
+      </c>
+      <c r="D94">
+        <v>371</v>
+      </c>
+      <c r="E94">
+        <v>362</v>
+      </c>
+      <c r="F94">
+        <v>9</v>
+      </c>
+      <c r="G94">
+        <v>341</v>
+      </c>
+      <c r="H94">
+        <v>335</v>
+      </c>
+      <c r="I94">
+        <v>6</v>
+      </c>
+      <c r="J94">
+        <v>0.91913746630727766</v>
+      </c>
+      <c r="K94">
+        <v>0.925414364640884</v>
+      </c>
+      <c r="L94">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="M94">
         <f t="shared" si="6"/>
-        <v>0.23226328567574858</v>
-      </c>
-      <c r="O93">
+        <v>0.2505510653930933</v>
+      </c>
+      <c r="N94">
         <f t="shared" si="7"/>
-        <v>0.23987450085567599</v>
-      </c>
-      <c r="P93">
+        <v>0.26440410418310972</v>
+      </c>
+      <c r="O94">
         <f t="shared" si="8"/>
-        <v>9.950248756218906E-2</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A94">
-        <v>4552</v>
-      </c>
-      <c r="B94">
-        <v>3707</v>
-      </c>
-      <c r="C94">
-        <v>3506</v>
-      </c>
-      <c r="D94">
-        <v>201</v>
-      </c>
-      <c r="E94">
-        <v>925</v>
-      </c>
-      <c r="F94">
-        <v>900</v>
-      </c>
-      <c r="G94">
-        <v>25</v>
-      </c>
-      <c r="H94">
-        <v>861</v>
-      </c>
-      <c r="I94">
-        <v>841</v>
-      </c>
-      <c r="J94">
-        <v>20</v>
-      </c>
-      <c r="K94">
-        <v>0.93081081081081085</v>
-      </c>
-      <c r="L94">
-        <v>0.93444444444444441</v>
-      </c>
-      <c r="M94">
-        <v>0.8</v>
-      </c>
-      <c r="N94">
+        <v>6.3829787234042548E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>1365</v>
+      </c>
+      <c r="B95">
+        <v>1268</v>
+      </c>
+      <c r="C95">
+        <v>97</v>
+      </c>
+      <c r="D95">
+        <v>395</v>
+      </c>
+      <c r="E95">
+        <v>386</v>
+      </c>
+      <c r="F95">
+        <v>9</v>
+      </c>
+      <c r="G95">
+        <v>358</v>
+      </c>
+      <c r="H95">
+        <v>350</v>
+      </c>
+      <c r="I95">
+        <v>8</v>
+      </c>
+      <c r="J95">
+        <v>0.90632911392405058</v>
+      </c>
+      <c r="K95">
+        <v>0.90673575129533679</v>
+      </c>
+      <c r="L95">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="M95">
         <f t="shared" si="6"/>
-        <v>0.23226328567574858</v>
-      </c>
-      <c r="O94">
+        <v>0.26227106227106228</v>
+      </c>
+      <c r="N95">
         <f t="shared" si="7"/>
-        <v>0.23987450085567599</v>
-      </c>
-      <c r="P94">
+        <v>0.27602523659305994</v>
+      </c>
+      <c r="O95">
         <f t="shared" si="8"/>
-        <v>9.950248756218906E-2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A95">
-        <v>4552</v>
-      </c>
-      <c r="B95">
-        <v>3707</v>
-      </c>
-      <c r="C95">
-        <v>3506</v>
-      </c>
-      <c r="D95">
-        <v>201</v>
-      </c>
-      <c r="E95">
-        <v>925</v>
-      </c>
-      <c r="F95">
-        <v>900</v>
-      </c>
-      <c r="G95">
-        <v>25</v>
-      </c>
-      <c r="H95">
-        <v>861</v>
-      </c>
-      <c r="I95">
-        <v>841</v>
-      </c>
-      <c r="J95">
-        <v>20</v>
-      </c>
-      <c r="K95">
-        <v>0.93081081081081085</v>
-      </c>
-      <c r="L95">
-        <v>0.93444444444444441</v>
-      </c>
-      <c r="M95">
-        <v>0.8</v>
-      </c>
-      <c r="N95">
+        <v>8.247422680412371E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>1356</v>
+      </c>
+      <c r="B96">
+        <v>1254</v>
+      </c>
+      <c r="C96">
+        <v>102</v>
+      </c>
+      <c r="D96">
+        <v>327</v>
+      </c>
+      <c r="E96">
+        <v>314</v>
+      </c>
+      <c r="F96">
+        <v>13</v>
+      </c>
+      <c r="G96">
+        <v>294</v>
+      </c>
+      <c r="H96">
+        <v>286</v>
+      </c>
+      <c r="I96">
+        <v>8</v>
+      </c>
+      <c r="J96">
+        <v>0.8990825688073395</v>
+      </c>
+      <c r="K96">
+        <v>0.91082802547770703</v>
+      </c>
+      <c r="L96">
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="M96">
         <f t="shared" si="6"/>
-        <v>0.23226328567574858</v>
-      </c>
-      <c r="O95">
+        <v>0.2168141592920354</v>
+      </c>
+      <c r="N96">
         <f t="shared" si="7"/>
-        <v>0.23987450085567599</v>
-      </c>
-      <c r="P95">
+        <v>0.22807017543859648</v>
+      </c>
+      <c r="O96">
         <f t="shared" si="8"/>
-        <v>9.950248756218906E-2</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A96">
-        <v>4552</v>
-      </c>
-      <c r="B96">
-        <v>3707</v>
-      </c>
-      <c r="C96">
-        <v>3506</v>
-      </c>
-      <c r="D96">
-        <v>201</v>
-      </c>
-      <c r="E96">
-        <v>925</v>
-      </c>
-      <c r="F96">
-        <v>900</v>
-      </c>
-      <c r="G96">
-        <v>25</v>
-      </c>
-      <c r="H96">
-        <v>861</v>
-      </c>
-      <c r="I96">
-        <v>841</v>
-      </c>
-      <c r="J96">
-        <v>20</v>
-      </c>
-      <c r="K96">
-        <v>0.93081081081081085</v>
-      </c>
-      <c r="L96">
-        <v>0.93444444444444441</v>
-      </c>
-      <c r="M96">
-        <v>0.8</v>
-      </c>
-      <c r="N96">
+        <v>7.8431372549019607E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>1346</v>
+      </c>
+      <c r="B97">
+        <v>1253</v>
+      </c>
+      <c r="C97">
+        <v>93</v>
+      </c>
+      <c r="D97">
+        <v>387</v>
+      </c>
+      <c r="E97">
+        <v>375</v>
+      </c>
+      <c r="F97">
+        <v>12</v>
+      </c>
+      <c r="G97">
+        <v>359</v>
+      </c>
+      <c r="H97">
+        <v>353</v>
+      </c>
+      <c r="I97">
+        <v>6</v>
+      </c>
+      <c r="J97">
+        <v>0.92764857881136953</v>
+      </c>
+      <c r="K97">
+        <v>0.94133333333333336</v>
+      </c>
+      <c r="L97">
+        <v>0.5</v>
+      </c>
+      <c r="M97">
         <f t="shared" si="6"/>
-        <v>0.23226328567574858</v>
-      </c>
-      <c r="O96">
+        <v>0.26671619613670133</v>
+      </c>
+      <c r="N97">
         <f t="shared" si="7"/>
-        <v>0.23987450085567599</v>
-      </c>
-      <c r="P96">
+        <v>0.28172386272944933</v>
+      </c>
+      <c r="O97">
         <f t="shared" si="8"/>
-        <v>9.950248756218906E-2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A97">
-        <v>4552</v>
-      </c>
-      <c r="B97">
-        <v>3707</v>
-      </c>
-      <c r="C97">
-        <v>3506</v>
-      </c>
-      <c r="D97">
-        <v>201</v>
-      </c>
-      <c r="E97">
-        <v>925</v>
-      </c>
-      <c r="F97">
-        <v>900</v>
-      </c>
-      <c r="G97">
-        <v>25</v>
-      </c>
-      <c r="H97">
-        <v>861</v>
-      </c>
-      <c r="I97">
-        <v>841</v>
-      </c>
-      <c r="J97">
-        <v>20</v>
-      </c>
-      <c r="K97">
-        <v>0.93081081081081085</v>
-      </c>
-      <c r="L97">
-        <v>0.93444444444444441</v>
-      </c>
-      <c r="M97">
-        <v>0.8</v>
-      </c>
-      <c r="N97">
+        <v>6.4516129032258063E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>1368</v>
+      </c>
+      <c r="B98">
+        <v>1277</v>
+      </c>
+      <c r="C98">
+        <v>91</v>
+      </c>
+      <c r="D98">
+        <v>367</v>
+      </c>
+      <c r="E98">
+        <v>356</v>
+      </c>
+      <c r="F98">
+        <v>11</v>
+      </c>
+      <c r="G98">
+        <v>325</v>
+      </c>
+      <c r="H98">
+        <v>317</v>
+      </c>
+      <c r="I98">
+        <v>8</v>
+      </c>
+      <c r="J98">
+        <v>0.88555858310626701</v>
+      </c>
+      <c r="K98">
+        <v>0.8904494382022472</v>
+      </c>
+      <c r="L98">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="M98">
         <f t="shared" si="6"/>
-        <v>0.23226328567574858</v>
-      </c>
-      <c r="O97">
+        <v>0.23757309941520469</v>
+      </c>
+      <c r="N98">
         <f t="shared" si="7"/>
-        <v>0.23987450085567599</v>
-      </c>
-      <c r="P97">
+        <v>0.24823805794831635</v>
+      </c>
+      <c r="O98">
         <f t="shared" si="8"/>
-        <v>9.950248756218906E-2</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+        <v>8.7912087912087919E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99">
-        <f>AVERAGE(A90:A97)</f>
-        <v>4552</v>
+        <v>1382</v>
       </c>
       <c r="B99">
-        <f t="shared" ref="B99:P99" si="9">AVERAGE(B90:B97)</f>
-        <v>3707</v>
+        <v>1268</v>
       </c>
       <c r="C99">
+        <v>114</v>
+      </c>
+      <c r="D99">
+        <v>383</v>
+      </c>
+      <c r="E99">
+        <v>369</v>
+      </c>
+      <c r="F99">
+        <v>14</v>
+      </c>
+      <c r="G99">
+        <v>339</v>
+      </c>
+      <c r="H99">
+        <v>328</v>
+      </c>
+      <c r="I99">
+        <v>11</v>
+      </c>
+      <c r="J99">
+        <v>0.88511749347258484</v>
+      </c>
+      <c r="K99">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="L99">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="M99">
+        <f t="shared" si="6"/>
+        <v>0.24529667149059334</v>
+      </c>
+      <c r="N99">
+        <f t="shared" si="7"/>
+        <v>0.25867507886435331</v>
+      </c>
+      <c r="O99">
+        <f t="shared" si="8"/>
+        <v>9.6491228070175433E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>1356</v>
+      </c>
+      <c r="B100">
+        <v>1249</v>
+      </c>
+      <c r="C100">
+        <v>107</v>
+      </c>
+      <c r="D100">
+        <v>334</v>
+      </c>
+      <c r="E100">
+        <v>327</v>
+      </c>
+      <c r="F100">
+        <v>7</v>
+      </c>
+      <c r="G100">
+        <v>303</v>
+      </c>
+      <c r="H100">
+        <v>297</v>
+      </c>
+      <c r="I100">
+        <v>6</v>
+      </c>
+      <c r="J100">
+        <v>0.90718562874251496</v>
+      </c>
+      <c r="K100">
+        <v>0.90825688073394495</v>
+      </c>
+      <c r="L100">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="M100">
+        <f t="shared" ref="M100:M102" si="9">G100/A100</f>
+        <v>0.22345132743362831</v>
+      </c>
+      <c r="N100">
+        <f t="shared" ref="N100:N102" si="10">H100/B100</f>
+        <v>0.2377902321857486</v>
+      </c>
+      <c r="O100">
+        <f t="shared" ref="O100:O102" si="11">I100/C100</f>
+        <v>5.6074766355140186E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>1324</v>
+      </c>
+      <c r="B101">
+        <v>1229</v>
+      </c>
+      <c r="C101">
+        <v>95</v>
+      </c>
+      <c r="D101">
+        <v>361</v>
+      </c>
+      <c r="E101">
+        <v>351</v>
+      </c>
+      <c r="F101">
+        <v>10</v>
+      </c>
+      <c r="G101">
+        <v>327</v>
+      </c>
+      <c r="H101">
+        <v>320</v>
+      </c>
+      <c r="I101">
+        <v>7</v>
+      </c>
+      <c r="J101">
+        <v>0.90581717451523547</v>
+      </c>
+      <c r="K101">
+        <v>0.9116809116809117</v>
+      </c>
+      <c r="L101">
+        <v>0.7</v>
+      </c>
+      <c r="M101">
         <f t="shared" si="9"/>
-        <v>3506</v>
-      </c>
-      <c r="D99">
+        <v>0.24697885196374622</v>
+      </c>
+      <c r="N101">
+        <f t="shared" si="10"/>
+        <v>0.26037428803905616</v>
+      </c>
+      <c r="O101">
+        <f t="shared" si="11"/>
+        <v>7.3684210526315783E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>1371</v>
+      </c>
+      <c r="B102">
+        <v>1278</v>
+      </c>
+      <c r="C102">
+        <v>93</v>
+      </c>
+      <c r="D102">
+        <v>365</v>
+      </c>
+      <c r="E102">
+        <v>354</v>
+      </c>
+      <c r="F102">
+        <v>11</v>
+      </c>
+      <c r="G102">
+        <v>321</v>
+      </c>
+      <c r="H102">
+        <v>314</v>
+      </c>
+      <c r="I102">
+        <v>7</v>
+      </c>
+      <c r="J102">
+        <v>0.8794520547945206</v>
+      </c>
+      <c r="K102">
+        <v>0.88700564971751417</v>
+      </c>
+      <c r="L102">
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="M102">
         <f t="shared" si="9"/>
-        <v>201</v>
-      </c>
-      <c r="E99">
-        <f t="shared" si="9"/>
-        <v>925</v>
-      </c>
-      <c r="F99">
-        <f t="shared" si="9"/>
-        <v>900</v>
-      </c>
-      <c r="G99">
-        <f t="shared" si="9"/>
-        <v>25</v>
-      </c>
-      <c r="H99">
-        <f t="shared" si="9"/>
-        <v>861</v>
-      </c>
-      <c r="I99">
-        <f t="shared" si="9"/>
-        <v>841</v>
-      </c>
-      <c r="J99">
-        <f t="shared" si="9"/>
-        <v>20</v>
-      </c>
-      <c r="K99">
-        <f t="shared" si="9"/>
-        <v>0.93081081081081074</v>
-      </c>
-      <c r="L99">
-        <f t="shared" si="9"/>
-        <v>0.93444444444444463</v>
-      </c>
-      <c r="M99">
-        <f t="shared" si="9"/>
-        <v>0.79999999999999993</v>
-      </c>
-      <c r="N99">
-        <f t="shared" si="9"/>
-        <v>0.23226328567574855</v>
-      </c>
-      <c r="O99">
-        <f t="shared" si="9"/>
-        <v>0.23987450085567599</v>
-      </c>
-      <c r="P99">
-        <f t="shared" si="9"/>
-        <v>9.950248756218906E-2</v>
-      </c>
-      <c r="Q99" t="s">
+        <v>0.23413566739606126</v>
+      </c>
+      <c r="N102">
+        <f t="shared" si="10"/>
+        <v>0.24569640062597808</v>
+      </c>
+      <c r="O102">
+        <f t="shared" si="11"/>
+        <v>7.5268817204301078E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A104" s="4">
+        <f>AVERAGE(A3:A103)</f>
+        <v>1359.06</v>
+      </c>
+      <c r="B104" s="4">
+        <f t="shared" ref="B104:O104" si="12">AVERAGE(B3:B103)</f>
+        <v>1259.98</v>
+      </c>
+      <c r="C104" s="4">
+        <f t="shared" si="12"/>
+        <v>99.08</v>
+      </c>
+      <c r="D104" s="4">
+        <f t="shared" si="12"/>
+        <v>361.74</v>
+      </c>
+      <c r="E104" s="4">
+        <f t="shared" si="12"/>
+        <v>351.48</v>
+      </c>
+      <c r="F104" s="4">
+        <f t="shared" si="12"/>
+        <v>10.26</v>
+      </c>
+      <c r="G104" s="4">
+        <f t="shared" si="12"/>
+        <v>326.86</v>
+      </c>
+      <c r="H104" s="4">
+        <f t="shared" si="12"/>
+        <v>319.91000000000003</v>
+      </c>
+      <c r="I104" s="4">
+        <f t="shared" si="12"/>
+        <v>6.95</v>
+      </c>
+      <c r="J104" s="3">
+        <f t="shared" si="12"/>
+        <v>0.90366759368958727</v>
+      </c>
+      <c r="K104" s="3">
+        <f t="shared" si="12"/>
+        <v>0.91024696588539056</v>
+      </c>
+      <c r="L104" s="3">
+        <f t="shared" si="12"/>
+        <v>0.69243303334092832</v>
+      </c>
+      <c r="M104" s="3">
+        <f t="shared" si="12"/>
+        <v>0.24053335525053501</v>
+      </c>
+      <c r="N104" s="3">
+        <f t="shared" si="12"/>
+        <v>0.25390604181954224</v>
+      </c>
+      <c r="O104" s="3">
+        <f t="shared" si="12"/>
+        <v>7.0069583734199969E-2</v>
+      </c>
+      <c r="P104" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A100">
-        <f>AVERAGE(A3:A89)</f>
-        <v>1820.5172413793102</v>
-      </c>
-      <c r="B100">
-        <f t="shared" ref="B100:P100" si="10">AVERAGE(B3:B89)</f>
-        <v>1359.3218390804598</v>
-      </c>
-      <c r="C100">
-        <f t="shared" si="10"/>
-        <v>1260.3563218390805</v>
-      </c>
-      <c r="D100">
-        <f t="shared" si="10"/>
-        <v>98.965517241379317</v>
-      </c>
-      <c r="E100">
-        <f t="shared" si="10"/>
-        <v>361.89655172413791</v>
-      </c>
-      <c r="F100">
-        <f t="shared" si="10"/>
-        <v>351.80459770114942</v>
-      </c>
-      <c r="G100">
-        <f t="shared" si="10"/>
-        <v>10.091954022988507</v>
-      </c>
-      <c r="H100">
-        <f t="shared" si="10"/>
-        <v>327.28735632183907</v>
-      </c>
-      <c r="I100">
-        <f t="shared" si="10"/>
-        <v>320.40229885057471</v>
-      </c>
-      <c r="J100">
-        <f t="shared" si="10"/>
-        <v>6.8850574712643677</v>
-      </c>
-      <c r="K100">
-        <f t="shared" si="10"/>
-        <v>0.90447429234530075</v>
-      </c>
-      <c r="L100">
-        <f t="shared" si="10"/>
-        <v>0.91081797205442516</v>
-      </c>
-      <c r="M100">
-        <f t="shared" si="10"/>
-        <v>0.69682391783117736</v>
-      </c>
-      <c r="N100">
-        <f t="shared" si="10"/>
-        <v>0.24080536671930963</v>
-      </c>
-      <c r="O100">
-        <f t="shared" si="10"/>
-        <v>0.25422548142218399</v>
-      </c>
-      <c r="P100">
-        <f t="shared" si="10"/>
-        <v>6.9528877831974464E-2</v>
-      </c>
-      <c r="Q100" t="s">
-        <v>17</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:P2" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P97">
-      <sortCondition ref="A2"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A2:O2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>